--- a/results/NDDHO N_xi Data [T_xi_len_s=25, Qs=[20, 40, 60, 80, 100], int 25ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
+++ b/results/NDDHO N_xi Data [T_xi_len_s=25, Qs=[20, 40, 60, 80, 100], int 25ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
@@ -518,7 +518,7 @@
         <v>1000</v>
       </c>
       <c r="C2" t="n">
-        <v>999.0795310852835</v>
+        <v>998.4225013206049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>344.3984647431471</v>
+        <v>324.2115102359805</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3443984647431471</v>
+        <v>0.3242115102359805</v>
       </c>
       <c r="G2" t="n">
-        <v>24.3435423437702</v>
+        <v>25.21228877105639</v>
       </c>
       <c r="H2" t="n">
-        <v>5.174153290861374e-13</v>
+        <v>5.063101870949051e-13</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
         <v>1000</v>
       </c>
       <c r="C3" t="n">
-        <v>999.0795310852835</v>
+        <v>998.4225013206049</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -584,16 +584,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>307.0099953164986</v>
+        <v>293.6304919017555</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3070099953164986</v>
+        <v>0.2936304919017556</v>
       </c>
       <c r="G3" t="n">
-        <v>24.3435423437702</v>
+        <v>25.21228877105639</v>
       </c>
       <c r="H3" t="n">
-        <v>5.174153290861374e-13</v>
+        <v>5.063101870949051e-13</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         <v>1000</v>
       </c>
       <c r="C4" t="n">
-        <v>998.9886074710256</v>
+        <v>999.9759243472744</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>335.3969927873744</v>
+        <v>338.3069528000227</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3353969927873744</v>
+        <v>0.3383069528000227</v>
       </c>
       <c r="G4" t="n">
-        <v>25.89973846334994</v>
+        <v>24.261465265354</v>
       </c>
       <c r="H4" t="n">
-        <v>5.091931995782508e-13</v>
+        <v>5.222260022042793e-13</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         <v>1000</v>
       </c>
       <c r="C5" t="n">
-        <v>998.9886074710256</v>
+        <v>999.9759243472744</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>301.9461101224232</v>
+        <v>303.6852257465633</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3019461101224232</v>
+        <v>0.3036852257465633</v>
       </c>
       <c r="G5" t="n">
-        <v>25.89973846334994</v>
+        <v>24.261465265354</v>
       </c>
       <c r="H5" t="n">
-        <v>5.091931995782508e-13</v>
+        <v>5.222260022042793e-13</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>1000</v>
       </c>
       <c r="C6" t="n">
-        <v>999.7173258476042</v>
+        <v>999.0494972283943</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>347.6077448039775</v>
+        <v>332.9338414789473</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3476077448039775</v>
+        <v>0.3329338414789473</v>
       </c>
       <c r="G6" t="n">
-        <v>23.40700997589546</v>
+        <v>25.4980343386911</v>
       </c>
       <c r="H6" t="n">
-        <v>5.130129922181231e-13</v>
+        <v>5.021638925435335e-13</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>1000</v>
       </c>
       <c r="C7" t="n">
-        <v>999.7173258476042</v>
+        <v>999.0494972283943</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>316.7787527589069</v>
+        <v>300.1741357310272</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3167787527589069</v>
+        <v>0.3001741357310272</v>
       </c>
       <c r="G7" t="n">
-        <v>23.40700997589546</v>
+        <v>25.4980343386911</v>
       </c>
       <c r="H7" t="n">
-        <v>5.130129922181231e-13</v>
+        <v>5.021638925435335e-13</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>1000</v>
       </c>
       <c r="C8" t="n">
-        <v>1000.026681792667</v>
+        <v>999.9750566019438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -874,16 +874,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>335.4792862893323</v>
+        <v>329.7901950879331</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3354792862893323</v>
+        <v>0.3297901950879331</v>
       </c>
       <c r="G8" t="n">
-        <v>25.35523017333661</v>
+        <v>25.09819578137034</v>
       </c>
       <c r="H8" t="n">
-        <v>5.161900832630684e-13</v>
+        <v>5.152572355887173e-13</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>1000</v>
       </c>
       <c r="C9" t="n">
-        <v>1000.026681792667</v>
+        <v>999.9750566019438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>303.6577265721101</v>
+        <v>305.6066079239947</v>
       </c>
       <c r="F9" t="n">
-        <v>0.30365772657211</v>
+        <v>0.3056066079239947</v>
       </c>
       <c r="G9" t="n">
-        <v>25.35523017333661</v>
+        <v>25.09819578137034</v>
       </c>
       <c r="H9" t="n">
-        <v>5.161900832630684e-13</v>
+        <v>5.152572355887173e-13</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>1000</v>
       </c>
       <c r="C10" t="n">
-        <v>998.8814359596405</v>
+        <v>999.6494893209095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>332.9195948734663</v>
+        <v>339.3384729832568</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3329195948734663</v>
+        <v>0.3393384729832569</v>
       </c>
       <c r="G10" t="n">
-        <v>24.55634267843893</v>
+        <v>24.51486889240477</v>
       </c>
       <c r="H10" t="n">
-        <v>5.143751408784861e-13</v>
+        <v>5.161824790122076e-13</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>1000</v>
       </c>
       <c r="C11" t="n">
-        <v>998.8814359596405</v>
+        <v>999.6494893209095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>304.209144527935</v>
+        <v>303.6863755767321</v>
       </c>
       <c r="F11" t="n">
-        <v>0.304209144527935</v>
+        <v>0.3036863755767321</v>
       </c>
       <c r="G11" t="n">
-        <v>24.55634267843893</v>
+        <v>24.51486889240477</v>
       </c>
       <c r="H11" t="n">
-        <v>5.143751408784861e-13</v>
+        <v>5.161824790122076e-13</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>1000</v>
       </c>
       <c r="C12" t="n">
-        <v>999.5437058776831</v>
+        <v>999.829278690319</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>333.8509964891105</v>
+        <v>335.1742013862393</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3338509964891105</v>
+        <v>0.3351742013862393</v>
       </c>
       <c r="G12" t="n">
-        <v>24.93776010157239</v>
+        <v>25.30706763069399</v>
       </c>
       <c r="H12" t="n">
-        <v>5.275051404065631e-13</v>
+        <v>5.034430882454177e-13</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>1000</v>
       </c>
       <c r="C13" t="n">
-        <v>999.5437058776831</v>
+        <v>999.829278690319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1164,16 +1164,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>306.1393220381791</v>
+        <v>301.0633818638737</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3061393220381791</v>
+        <v>0.3010633818638737</v>
       </c>
       <c r="G13" t="n">
-        <v>24.93776010157239</v>
+        <v>25.30706763069399</v>
       </c>
       <c r="H13" t="n">
-        <v>5.275051404065631e-13</v>
+        <v>5.034430882454177e-13</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>1000</v>
       </c>
       <c r="C14" t="n">
-        <v>1000.344073794479</v>
+        <v>998.4421251732645</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1222,16 +1222,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>338.4219923314973</v>
+        <v>333.9294211508277</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3384219923314973</v>
+        <v>0.3339294211508277</v>
       </c>
       <c r="G14" t="n">
-        <v>25.38427339001288</v>
+        <v>25.51625561564435</v>
       </c>
       <c r="H14" t="n">
-        <v>5.023226772840642e-13</v>
+        <v>5.002301131924765e-13</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>1000</v>
       </c>
       <c r="C15" t="n">
-        <v>1000.344073794479</v>
+        <v>998.4421251732645</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>302.7854289745814</v>
+        <v>307.8956488836439</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3027854289745813</v>
+        <v>0.3078956488836439</v>
       </c>
       <c r="G15" t="n">
-        <v>25.38427339001288</v>
+        <v>25.51625561564435</v>
       </c>
       <c r="H15" t="n">
-        <v>5.023226772840642e-13</v>
+        <v>5.002301131924765e-13</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>1000</v>
       </c>
       <c r="C16" t="n">
-        <v>999.3771365242177</v>
+        <v>999.0049633756722</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1338,16 +1338,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>340.0208786135767</v>
+        <v>338.8144180209079</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3400208786135767</v>
+        <v>0.3388144180209078</v>
       </c>
       <c r="G16" t="n">
-        <v>24.91288996012657</v>
+        <v>23.9887613787225</v>
       </c>
       <c r="H16" t="n">
-        <v>5.212257881887252e-13</v>
+        <v>5.328426572868119e-13</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>1000</v>
       </c>
       <c r="C17" t="n">
-        <v>999.3771365242177</v>
+        <v>999.0049633756722</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1396,16 +1396,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308.6584442956003</v>
+        <v>305.1114880792545</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3086584442956003</v>
+        <v>0.3051114880792545</v>
       </c>
       <c r="G17" t="n">
-        <v>24.91288996012657</v>
+        <v>23.9887613787225</v>
       </c>
       <c r="H17" t="n">
-        <v>5.212257881887252e-13</v>
+        <v>5.328426572868119e-13</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>1000</v>
       </c>
       <c r="C18" t="n">
-        <v>999.0660305697063</v>
+        <v>999.4181209859004</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1454,16 +1454,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>328.7423040050542</v>
+        <v>330.7641931026336</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3287423040050542</v>
+        <v>0.3307641931026336</v>
       </c>
       <c r="G18" t="n">
-        <v>24.93738313475369</v>
+        <v>25.4413699468953</v>
       </c>
       <c r="H18" t="n">
-        <v>5.171756017845165e-13</v>
+        <v>5.079824640122996e-13</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>1000</v>
       </c>
       <c r="C19" t="n">
-        <v>999.0660305697063</v>
+        <v>999.4181209859004</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1512,16 +1512,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>302.3752984838594</v>
+        <v>297.9455147483727</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3023752984838594</v>
+        <v>0.2979455147483727</v>
       </c>
       <c r="G19" t="n">
-        <v>24.93738313475369</v>
+        <v>25.4413699468953</v>
       </c>
       <c r="H19" t="n">
-        <v>5.171756017845165e-13</v>
+        <v>5.079824640122996e-13</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>1000</v>
       </c>
       <c r="C20" t="n">
-        <v>998.8408143262411</v>
+        <v>999.1847951784196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1570,16 +1570,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>329.6602766804189</v>
+        <v>328.5201514436868</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3296602766804189</v>
+        <v>0.3285201514436868</v>
       </c>
       <c r="G20" t="n">
-        <v>25.27557404446894</v>
+        <v>24.97006194884822</v>
       </c>
       <c r="H20" t="n">
-        <v>4.994517924650164e-13</v>
+        <v>5.074487884714652e-13</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>1000</v>
       </c>
       <c r="C21" t="n">
-        <v>998.8408143262411</v>
+        <v>999.1847951784196</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>297.6840798414919</v>
+        <v>295.8265846913163</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2976840798414919</v>
+        <v>0.2958265846913163</v>
       </c>
       <c r="G21" t="n">
-        <v>25.27557404446894</v>
+        <v>24.97006194884822</v>
       </c>
       <c r="H21" t="n">
-        <v>4.994517924650164e-13</v>
+        <v>5.074487884714652e-13</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>1000</v>
       </c>
       <c r="C22" t="n">
-        <v>1000.098173152995</v>
+        <v>1000.514473332035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>487.9229937697961</v>
+        <v>467.9794151796936</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4879229937697961</v>
+        <v>0.4679794151796936</v>
       </c>
       <c r="G22" t="n">
-        <v>13.03137430278162</v>
+        <v>12.53507186614564</v>
       </c>
       <c r="H22" t="n">
-        <v>1.997236612501982e-12</v>
+        <v>2.060242539748199e-12</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>1000</v>
       </c>
       <c r="C23" t="n">
-        <v>1000.098173152995</v>
+        <v>1000.514473332035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1744,16 +1744,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>440.9933676765099</v>
+        <v>430.8674914986371</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4409933676765099</v>
+        <v>0.4308674914986371</v>
       </c>
       <c r="G23" t="n">
-        <v>13.03137430278162</v>
+        <v>12.53507186614564</v>
       </c>
       <c r="H23" t="n">
-        <v>1.997236612501982e-12</v>
+        <v>2.060242539748199e-12</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>1000</v>
       </c>
       <c r="C24" t="n">
-        <v>999.8336015685405</v>
+        <v>1000.187579805119</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1802,16 +1802,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>471.6257245227154</v>
+        <v>492.5709087462378</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4716257245227154</v>
+        <v>0.4925709087462378</v>
       </c>
       <c r="G24" t="n">
-        <v>12.94646520567119</v>
+        <v>12.60420839802524</v>
       </c>
       <c r="H24" t="n">
-        <v>2.036785067274509e-12</v>
+        <v>2.073559112908982e-12</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>1000</v>
       </c>
       <c r="C25" t="n">
-        <v>999.8336015685405</v>
+        <v>1000.187579805119</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1860,16 +1860,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>436.9350998309525</v>
+        <v>426.4846196853222</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4369350998309525</v>
+        <v>0.4264846196853222</v>
       </c>
       <c r="G25" t="n">
-        <v>12.94646520567119</v>
+        <v>12.60420839802524</v>
       </c>
       <c r="H25" t="n">
-        <v>2.036785067274509e-12</v>
+        <v>2.073559112908982e-12</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>1000</v>
       </c>
       <c r="C26" t="n">
-        <v>999.7809784694595</v>
+        <v>1000.258461868115</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1918,16 +1918,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>489.711762835243</v>
+        <v>489.1381381523923</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4897117628352429</v>
+        <v>0.4891381381523923</v>
       </c>
       <c r="G26" t="n">
-        <v>12.76161669867182</v>
+        <v>12.42069091691751</v>
       </c>
       <c r="H26" t="n">
-        <v>2.096085034830536e-12</v>
+        <v>2.062480020590408e-12</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>1000</v>
       </c>
       <c r="C27" t="n">
-        <v>999.7809784694595</v>
+        <v>1000.258461868115</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1976,16 +1976,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>424.3109618070129</v>
+        <v>432.1799929364099</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4243109618070128</v>
+        <v>0.4321799929364099</v>
       </c>
       <c r="G27" t="n">
-        <v>12.76161669867182</v>
+        <v>12.42069091691751</v>
       </c>
       <c r="H27" t="n">
-        <v>2.096085034830536e-12</v>
+        <v>2.062480020590408e-12</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>1000</v>
       </c>
       <c r="C28" t="n">
-        <v>999.9746050880021</v>
+        <v>999.7457886096983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2034,16 +2034,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>502.5793616675174</v>
+        <v>484.4666848509669</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5025793616675174</v>
+        <v>0.4844666848509669</v>
       </c>
       <c r="G28" t="n">
-        <v>12.96674966626801</v>
+        <v>12.75811605571242</v>
       </c>
       <c r="H28" t="n">
-        <v>2.004992387156398e-12</v>
+        <v>2.052021778382174e-12</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>1000</v>
       </c>
       <c r="C29" t="n">
-        <v>999.9746050880021</v>
+        <v>999.7457886096983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2092,16 +2092,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>435.9778954672439</v>
+        <v>445.1894053102567</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4359778954672439</v>
+        <v>0.4451894053102567</v>
       </c>
       <c r="G29" t="n">
-        <v>12.96674966626801</v>
+        <v>12.75811605571242</v>
       </c>
       <c r="H29" t="n">
-        <v>2.004992387156398e-12</v>
+        <v>2.052021778382174e-12</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>1000</v>
       </c>
       <c r="C30" t="n">
-        <v>999.4396596597254</v>
+        <v>999.7594691322312</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2150,16 +2150,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>485.327306185129</v>
+        <v>491.9419586665282</v>
       </c>
       <c r="F30" t="n">
-        <v>0.485327306185129</v>
+        <v>0.4919419586665282</v>
       </c>
       <c r="G30" t="n">
-        <v>12.63651722183536</v>
+        <v>12.59622635363043</v>
       </c>
       <c r="H30" t="n">
-        <v>2.032998466751679e-12</v>
+        <v>2.024147912300429e-12</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>1000</v>
       </c>
       <c r="C31" t="n">
-        <v>999.4396596597254</v>
+        <v>999.7594691322312</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>429.9977675892797</v>
+        <v>443.4728645650041</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4299977675892797</v>
+        <v>0.4434728645650041</v>
       </c>
       <c r="G31" t="n">
-        <v>12.63651722183536</v>
+        <v>12.59622635363043</v>
       </c>
       <c r="H31" t="n">
-        <v>2.032998466751679e-12</v>
+        <v>2.024147912300429e-12</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>1000</v>
       </c>
       <c r="C32" t="n">
-        <v>1000.042298284201</v>
+        <v>999.8880137775003</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2266,16 +2266,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>486.7297019527095</v>
+        <v>503.8050963611445</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4867297019527095</v>
+        <v>0.5038050963611445</v>
       </c>
       <c r="G32" t="n">
-        <v>12.21632857065105</v>
+        <v>12.15702021471945</v>
       </c>
       <c r="H32" t="n">
-        <v>2.10838847744527e-12</v>
+        <v>2.067406771146633e-12</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>1000</v>
       </c>
       <c r="C33" t="n">
-        <v>1000.042298284201</v>
+        <v>999.8880137775003</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2324,16 +2324,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>431.6329065158517</v>
+        <v>460.910022918774</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4316329065158517</v>
+        <v>0.460910022918774</v>
       </c>
       <c r="G33" t="n">
-        <v>12.21632857065105</v>
+        <v>12.15702021471945</v>
       </c>
       <c r="H33" t="n">
-        <v>2.10838847744527e-12</v>
+        <v>2.067406771146633e-12</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>1000</v>
       </c>
       <c r="C34" t="n">
-        <v>1000.204910391039</v>
+        <v>999.4398729359654</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>480.8766737255214</v>
+        <v>510.0609579835599</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4808766737255213</v>
+        <v>0.5100609579835599</v>
       </c>
       <c r="G34" t="n">
-        <v>13.19159347342281</v>
+        <v>12.03700976465027</v>
       </c>
       <c r="H34" t="n">
-        <v>2.031627900541055e-12</v>
+        <v>2.111645707286435e-12</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>1000</v>
       </c>
       <c r="C35" t="n">
-        <v>1000.204910391039</v>
+        <v>999.4398729359654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2440,16 +2440,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>431.6298227782372</v>
+        <v>455.3760575690588</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4316298227782371</v>
+        <v>0.4553760575690588</v>
       </c>
       <c r="G35" t="n">
-        <v>13.19159347342281</v>
+        <v>12.03700976465027</v>
       </c>
       <c r="H35" t="n">
-        <v>2.031627900541055e-12</v>
+        <v>2.111645707286435e-12</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>1000</v>
       </c>
       <c r="C36" t="n">
-        <v>999.8209029789939</v>
+        <v>1000.258143404896</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2498,16 +2498,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>478.8499757585675</v>
+        <v>464.908074867994</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4788499757585675</v>
+        <v>0.464908074867994</v>
       </c>
       <c r="G36" t="n">
-        <v>12.26325904554745</v>
+        <v>13.32374123773442</v>
       </c>
       <c r="H36" t="n">
-        <v>2.006185544616547e-12</v>
+        <v>1.939644026621721e-12</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>1000</v>
       </c>
       <c r="C37" t="n">
-        <v>999.8209029789939</v>
+        <v>1000.258143404896</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2556,16 +2556,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>428.902209709275</v>
+        <v>418.5132721239805</v>
       </c>
       <c r="F37" t="n">
-        <v>0.428902209709275</v>
+        <v>0.4185132721239805</v>
       </c>
       <c r="G37" t="n">
-        <v>12.26325904554745</v>
+        <v>13.32374123773442</v>
       </c>
       <c r="H37" t="n">
-        <v>2.006185544616547e-12</v>
+        <v>1.939644026621721e-12</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>1000</v>
       </c>
       <c r="C38" t="n">
-        <v>999.2185922282849</v>
+        <v>999.7921259713294</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2614,16 +2614,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>501.3312582052573</v>
+        <v>492.4423616314937</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5013312582052573</v>
+        <v>0.4924423616314937</v>
       </c>
       <c r="G38" t="n">
-        <v>12.52007481377767</v>
+        <v>11.6343073542337</v>
       </c>
       <c r="H38" t="n">
-        <v>2.120274991232854e-12</v>
+        <v>2.121455638784538e-12</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1000</v>
       </c>
       <c r="C39" t="n">
-        <v>999.2185922282849</v>
+        <v>999.7921259713294</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>447.0058859754187</v>
+        <v>447.872485403656</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4470058859754187</v>
+        <v>0.447872485403656</v>
       </c>
       <c r="G39" t="n">
-        <v>12.52007481377767</v>
+        <v>11.6343073542337</v>
       </c>
       <c r="H39" t="n">
-        <v>2.120274991232854e-12</v>
+        <v>2.121455638784538e-12</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>1000</v>
       </c>
       <c r="C40" t="n">
-        <v>1000.137910477665</v>
+        <v>1000.255597414062</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2730,16 +2730,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>499.1410510965321</v>
+        <v>510.2790563637733</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4991410510965321</v>
+        <v>0.5102790563637734</v>
       </c>
       <c r="G40" t="n">
-        <v>11.95627106560033</v>
+        <v>12.11760309843881</v>
       </c>
       <c r="H40" t="n">
-        <v>2.171262998808419e-12</v>
+        <v>2.216224167574203e-12</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>1000</v>
       </c>
       <c r="C41" t="n">
-        <v>1000.137910477665</v>
+        <v>1000.255597414062</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2788,16 +2788,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>458.4019934010466</v>
+        <v>452.1351327087556</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4584019934010466</v>
+        <v>0.4521351327087556</v>
       </c>
       <c r="G41" t="n">
-        <v>11.95627106560033</v>
+        <v>12.11760309843881</v>
       </c>
       <c r="H41" t="n">
-        <v>2.171262998808419e-12</v>
+        <v>2.216224167574203e-12</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>1000</v>
       </c>
       <c r="C42" t="n">
-        <v>999.9760112086756</v>
+        <v>999.6623943751084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>614.0307760196664</v>
+        <v>556.7503940781398</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6140307760196664</v>
+        <v>0.5567503940781399</v>
       </c>
       <c r="G42" t="n">
-        <v>8.972301365693362</v>
+        <v>8.884132490455888</v>
       </c>
       <c r="H42" t="n">
-        <v>4.480676003192514e-12</v>
+        <v>4.425087119162017e-12</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>1000</v>
       </c>
       <c r="C43" t="n">
-        <v>999.9760112086756</v>
+        <v>999.6623943751084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>545.8291476701437</v>
+        <v>521.6705904126344</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5458291476701437</v>
+        <v>0.5216705904126344</v>
       </c>
       <c r="G43" t="n">
-        <v>8.972301365693362</v>
+        <v>8.884132490455888</v>
       </c>
       <c r="H43" t="n">
-        <v>4.480676003192514e-12</v>
+        <v>4.425087119162017e-12</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>1000</v>
       </c>
       <c r="C44" t="n">
-        <v>1000.048094165015</v>
+        <v>1000.021465119558</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2962,16 +2962,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>575.8069142281277</v>
+        <v>611.4669132902549</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5758069142281277</v>
+        <v>0.6114669132902548</v>
       </c>
       <c r="G44" t="n">
-        <v>8.992377730886654</v>
+        <v>8.412610916048999</v>
       </c>
       <c r="H44" t="n">
-        <v>4.364678038345593e-12</v>
+        <v>4.543895864037508e-12</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>1000</v>
       </c>
       <c r="C45" t="n">
-        <v>1000.048094165015</v>
+        <v>1000.021465119558</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3020,16 +3020,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>514.2129224012563</v>
+        <v>553.0944326108036</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5142129224012563</v>
+        <v>0.5530944326108036</v>
       </c>
       <c r="G45" t="n">
-        <v>8.992377730886654</v>
+        <v>8.412610916048999</v>
       </c>
       <c r="H45" t="n">
-        <v>4.364678038345593e-12</v>
+        <v>4.543895864037508e-12</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>1000</v>
       </c>
       <c r="C46" t="n">
-        <v>999.7444324884721</v>
+        <v>999.6036792371169</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3078,16 +3078,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>622.9300931984901</v>
+        <v>632.3161902887689</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6229300931984901</v>
+        <v>0.6323161902887688</v>
       </c>
       <c r="G46" t="n">
-        <v>8.156698568278642</v>
+        <v>8.499344988717899</v>
       </c>
       <c r="H46" t="n">
-        <v>4.587397274265273e-12</v>
+        <v>4.56842701477337e-12</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>1000</v>
       </c>
       <c r="C47" t="n">
-        <v>999.7444324884721</v>
+        <v>999.6036792371169</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3136,16 +3136,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>547.3510545364982</v>
+        <v>562.3527432746243</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5473510545364981</v>
+        <v>0.5623527432746244</v>
       </c>
       <c r="G47" t="n">
-        <v>8.156698568278642</v>
+        <v>8.499344988717899</v>
       </c>
       <c r="H47" t="n">
-        <v>4.587397274265273e-12</v>
+        <v>4.56842701477337e-12</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>1000</v>
       </c>
       <c r="C48" t="n">
-        <v>1000.177644771783</v>
+        <v>999.2225566246392</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3194,16 +3194,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>588.9818289452302</v>
+        <v>604.6664313386344</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5889818289452302</v>
+        <v>0.6046664313386344</v>
       </c>
       <c r="G48" t="n">
-        <v>8.347199317529665</v>
+        <v>8.630591748049056</v>
       </c>
       <c r="H48" t="n">
-        <v>4.673752284787559e-12</v>
+        <v>4.507145231756666e-12</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>1000</v>
       </c>
       <c r="C49" t="n">
-        <v>1000.177644771783</v>
+        <v>999.2225566246392</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3252,16 +3252,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>539.566396666945</v>
+        <v>549.852368417972</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5395663966669451</v>
+        <v>0.549852368417972</v>
       </c>
       <c r="G49" t="n">
-        <v>8.347199317529665</v>
+        <v>8.630591748049056</v>
       </c>
       <c r="H49" t="n">
-        <v>4.673752284787559e-12</v>
+        <v>4.507145231756666e-12</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>1000</v>
       </c>
       <c r="C50" t="n">
-        <v>999.7458014727944</v>
+        <v>999.9167947662307</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3310,16 +3310,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>631.9997036867616</v>
+        <v>588.6070426522972</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6319997036867616</v>
+        <v>0.5886070426522972</v>
       </c>
       <c r="G50" t="n">
-        <v>8.843022205298219</v>
+        <v>8.561017793992901</v>
       </c>
       <c r="H50" t="n">
-        <v>4.508973383248733e-12</v>
+        <v>4.462083994027301e-12</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>1000</v>
       </c>
       <c r="C51" t="n">
-        <v>999.7458014727944</v>
+        <v>999.9167947662307</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3368,16 +3368,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>559.4646518142176</v>
+        <v>541.7257631972138</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5594646518142177</v>
+        <v>0.5417257631972139</v>
       </c>
       <c r="G51" t="n">
-        <v>8.843022205298219</v>
+        <v>8.561017793992901</v>
       </c>
       <c r="H51" t="n">
-        <v>4.508973383248733e-12</v>
+        <v>4.462083994027301e-12</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>1000</v>
       </c>
       <c r="C52" t="n">
-        <v>999.840575790601</v>
+        <v>1000.148513176693</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3426,16 +3426,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>628.9056099041462</v>
+        <v>591.6941144010618</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6289056099041462</v>
+        <v>0.5916941144010618</v>
       </c>
       <c r="G52" t="n">
-        <v>8.289526913745039</v>
+        <v>8.846877636380791</v>
       </c>
       <c r="H52" t="n">
-        <v>4.580878207961126e-12</v>
+        <v>4.262420743375341e-12</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>1000</v>
       </c>
       <c r="C53" t="n">
-        <v>999.840575790601</v>
+        <v>1000.148513176693</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3484,16 +3484,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>567.8595935585172</v>
+        <v>532.0282444141674</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5678595935585172</v>
+        <v>0.5320282444141674</v>
       </c>
       <c r="G53" t="n">
-        <v>8.289526913745039</v>
+        <v>8.846877636380791</v>
       </c>
       <c r="H53" t="n">
-        <v>4.580878207961126e-12</v>
+        <v>4.262420743375341e-12</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>1000</v>
       </c>
       <c r="C54" t="n">
-        <v>999.4142097585607</v>
+        <v>999.6022731466114</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3542,16 +3542,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>573.8298746968522</v>
+        <v>632.1629594240937</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5738298746968522</v>
+        <v>0.6321629594240937</v>
       </c>
       <c r="G54" t="n">
-        <v>8.601513176547753</v>
+        <v>7.968127143621341</v>
       </c>
       <c r="H54" t="n">
-        <v>4.572089053736817e-12</v>
+        <v>4.789349253955437e-12</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>1000</v>
       </c>
       <c r="C55" t="n">
-        <v>999.4142097585607</v>
+        <v>999.6022731466114</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3600,16 +3600,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>519.9532353796146</v>
+        <v>570.0851471456737</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5199532353796146</v>
+        <v>0.5700851471456737</v>
       </c>
       <c r="G55" t="n">
-        <v>8.601513176547753</v>
+        <v>7.968127143621341</v>
       </c>
       <c r="H55" t="n">
-        <v>4.572089053736817e-12</v>
+        <v>4.789349253955437e-12</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>1000</v>
       </c>
       <c r="C56" t="n">
-        <v>999.9507071641788</v>
+        <v>999.3996376998122</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3658,16 +3658,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>578.9150327025731</v>
+        <v>608.7130930352369</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5789150327025731</v>
+        <v>0.6087130930352369</v>
       </c>
       <c r="G56" t="n">
-        <v>8.964479788897211</v>
+        <v>8.687944518936808</v>
       </c>
       <c r="H56" t="n">
-        <v>4.428720293110508e-12</v>
+        <v>4.383500678076688e-12</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>1000</v>
       </c>
       <c r="C57" t="n">
-        <v>999.9507071641788</v>
+        <v>999.3996376998122</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3716,16 +3716,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>526.6581636738697</v>
+        <v>575.0914148393348</v>
       </c>
       <c r="F57" t="n">
-        <v>0.5266581636738698</v>
+        <v>0.5750914148393348</v>
       </c>
       <c r="G57" t="n">
-        <v>8.964479788897211</v>
+        <v>8.687944518936808</v>
       </c>
       <c r="H57" t="n">
-        <v>4.428720293110508e-12</v>
+        <v>4.383500678076688e-12</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>1000</v>
       </c>
       <c r="C58" t="n">
-        <v>999.7207018228959</v>
+        <v>999.7367102065431</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3774,16 +3774,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>611.8203816799605</v>
+        <v>625.3066196538689</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6118203816799606</v>
+        <v>0.6253066196538689</v>
       </c>
       <c r="G58" t="n">
-        <v>9.027894564165647</v>
+        <v>8.079223118977133</v>
       </c>
       <c r="H58" t="n">
-        <v>4.212443630452457e-12</v>
+        <v>4.865997823359862e-12</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>1000</v>
       </c>
       <c r="C59" t="n">
-        <v>999.7207018228959</v>
+        <v>999.7367102065431</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>543.1540388427227</v>
+        <v>560.2000166605973</v>
       </c>
       <c r="F59" t="n">
-        <v>0.5431540388427227</v>
+        <v>0.5602000166605973</v>
       </c>
       <c r="G59" t="n">
-        <v>9.027894564165647</v>
+        <v>8.079223118977133</v>
       </c>
       <c r="H59" t="n">
-        <v>4.212443630452457e-12</v>
+        <v>4.865997823359862e-12</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>1000</v>
       </c>
       <c r="C60" t="n">
-        <v>1000.401049912279</v>
+        <v>999.8651741725141</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>623.905257869655</v>
+        <v>637.6226593782111</v>
       </c>
       <c r="F60" t="n">
-        <v>0.623905257869655</v>
+        <v>0.6376226593782111</v>
       </c>
       <c r="G60" t="n">
-        <v>8.330592673801085</v>
+        <v>8.881424730668568</v>
       </c>
       <c r="H60" t="n">
-        <v>4.523696820619554e-12</v>
+        <v>4.550511115451748e-12</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>1000</v>
       </c>
       <c r="C61" t="n">
-        <v>1000.401049912279</v>
+        <v>999.8651741725141</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3948,16 +3948,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>546.9010182640189</v>
+        <v>573.636629357879</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5469010182640189</v>
+        <v>0.573636629357879</v>
       </c>
       <c r="G61" t="n">
-        <v>8.330592673801085</v>
+        <v>8.881424730668568</v>
       </c>
       <c r="H61" t="n">
-        <v>4.523696820619554e-12</v>
+        <v>4.550511115451748e-12</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>1000</v>
       </c>
       <c r="C62" t="n">
-        <v>1000.194812539765</v>
+        <v>1000.059518464419</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4006,16 +4006,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>694.5247465280063</v>
+        <v>714.5197019152289</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6945247465280063</v>
+        <v>0.7145197019152288</v>
       </c>
       <c r="G62" t="n">
-        <v>6.253317243145512</v>
+        <v>6.574830277227479</v>
       </c>
       <c r="H62" t="n">
-        <v>8.086952772154858e-12</v>
+        <v>7.981232663003751e-12</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>1000</v>
       </c>
       <c r="C63" t="n">
-        <v>1000.194812539765</v>
+        <v>1000.059518464419</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4064,16 +4064,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>650.0510758356342</v>
+        <v>638.136393389658</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6500510758356342</v>
+        <v>0.638136393389658</v>
       </c>
       <c r="G63" t="n">
-        <v>6.253317243145512</v>
+        <v>6.574830277227479</v>
       </c>
       <c r="H63" t="n">
-        <v>8.086952772154858e-12</v>
+        <v>7.981232663003751e-12</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>1000</v>
       </c>
       <c r="C64" t="n">
-        <v>999.7439217841336</v>
+        <v>1000.343543438228</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4122,16 +4122,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>680.1043740389302</v>
+        <v>729.5467432864536</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6801043740389302</v>
+        <v>0.7295467432864536</v>
       </c>
       <c r="G64" t="n">
-        <v>6.409175201945789</v>
+        <v>6.344303055399328</v>
       </c>
       <c r="H64" t="n">
-        <v>7.793684037336111e-12</v>
+        <v>8.376132699933391e-12</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>1000</v>
       </c>
       <c r="C65" t="n">
-        <v>999.7439217841336</v>
+        <v>1000.343543438228</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4180,16 +4180,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>646.1377530802757</v>
+        <v>655.5857529536225</v>
       </c>
       <c r="F65" t="n">
-        <v>0.6461377530802758</v>
+        <v>0.6555857529536225</v>
       </c>
       <c r="G65" t="n">
-        <v>6.409175201945789</v>
+        <v>6.344303055399328</v>
       </c>
       <c r="H65" t="n">
-        <v>7.793684037336111e-12</v>
+        <v>8.376132699933391e-12</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>1000</v>
       </c>
       <c r="C66" t="n">
-        <v>1000.103791956285</v>
+        <v>1000.011955982668</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4238,16 +4238,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>747.3281048638329</v>
+        <v>737.0013838778123</v>
       </c>
       <c r="F66" t="n">
-        <v>0.7473281048638329</v>
+        <v>0.7370013838778122</v>
       </c>
       <c r="G66" t="n">
-        <v>5.843450989207042</v>
+        <v>6.308077783563384</v>
       </c>
       <c r="H66" t="n">
-        <v>8.51034258029183e-12</v>
+        <v>8.117641877438317e-12</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>1000</v>
       </c>
       <c r="C67" t="n">
-        <v>1000.103791956285</v>
+        <v>1000.011955982668</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4296,16 +4296,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>646.0975813648146</v>
+        <v>663.1191715990991</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6460975813648145</v>
+        <v>0.6631191715990991</v>
       </c>
       <c r="G67" t="n">
-        <v>5.843450989207042</v>
+        <v>6.308077783563384</v>
       </c>
       <c r="H67" t="n">
-        <v>8.51034258029183e-12</v>
+        <v>8.117641877438317e-12</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>1000</v>
       </c>
       <c r="C68" t="n">
-        <v>1000.035321535357</v>
+        <v>999.8321249034933</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4354,16 +4354,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>688.3601660592743</v>
+        <v>758.2486169217447</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6883601660592743</v>
+        <v>0.7582486169217446</v>
       </c>
       <c r="G68" t="n">
-        <v>6.570681499768352</v>
+        <v>6.252265955335007</v>
       </c>
       <c r="H68" t="n">
-        <v>8.077593308001922e-12</v>
+        <v>8.017840860118325e-12</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>1000</v>
       </c>
       <c r="C69" t="n">
-        <v>1000.035321535357</v>
+        <v>999.8321249034933</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4412,16 +4412,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>619.5525890992783</v>
+        <v>690.8303261601264</v>
       </c>
       <c r="F69" t="n">
-        <v>0.6195525890992784</v>
+        <v>0.6908303261601264</v>
       </c>
       <c r="G69" t="n">
-        <v>6.570681499768352</v>
+        <v>6.252265955335007</v>
       </c>
       <c r="H69" t="n">
-        <v>8.077593308001922e-12</v>
+        <v>8.017840860118325e-12</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>1000</v>
       </c>
       <c r="C70" t="n">
-        <v>999.7746874779448</v>
+        <v>999.4639053546425</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4470,16 +4470,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>698.5242882991176</v>
+        <v>735.8994731937661</v>
       </c>
       <c r="F70" t="n">
-        <v>0.6985242882991176</v>
+        <v>0.735899473193766</v>
       </c>
       <c r="G70" t="n">
-        <v>6.771512638635842</v>
+        <v>6.556270627421423</v>
       </c>
       <c r="H70" t="n">
-        <v>7.856058878856217e-12</v>
+        <v>7.772879139039257e-12</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>1000</v>
       </c>
       <c r="C71" t="n">
-        <v>999.7746874779448</v>
+        <v>999.4639053546425</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4528,16 +4528,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>649.7360067250487</v>
+        <v>652.0828750193489</v>
       </c>
       <c r="F71" t="n">
-        <v>0.6497360067250487</v>
+        <v>0.6520828750193489</v>
       </c>
       <c r="G71" t="n">
-        <v>6.771512638635842</v>
+        <v>6.556270627421423</v>
       </c>
       <c r="H71" t="n">
-        <v>7.856058878856217e-12</v>
+        <v>7.772879139039257e-12</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>1000</v>
       </c>
       <c r="C72" t="n">
-        <v>1000.153570516733</v>
+        <v>1000.085432325466</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4586,16 +4586,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>713.561717758079</v>
+        <v>705.7979075653232</v>
       </c>
       <c r="F72" t="n">
-        <v>0.713561717758079</v>
+        <v>0.7057979075653231</v>
       </c>
       <c r="G72" t="n">
-        <v>6.618795435712532</v>
+        <v>6.397781984721444</v>
       </c>
       <c r="H72" t="n">
-        <v>7.824996215680516e-12</v>
+        <v>7.804798296009796e-12</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>1000</v>
       </c>
       <c r="C73" t="n">
-        <v>1000.153570516733</v>
+        <v>1000.085432325466</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4644,16 +4644,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>645.7857606078381</v>
+        <v>624.6774584698227</v>
       </c>
       <c r="F73" t="n">
-        <v>0.6457857606078381</v>
+        <v>0.6246774584698227</v>
       </c>
       <c r="G73" t="n">
-        <v>6.618795435712532</v>
+        <v>6.397781984721444</v>
       </c>
       <c r="H73" t="n">
-        <v>7.824996215680516e-12</v>
+        <v>7.804798296009796e-12</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>1000</v>
       </c>
       <c r="C74" t="n">
-        <v>999.8103074968528</v>
+        <v>1000.379766952949</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4702,16 +4702,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>788.1713330213294</v>
+        <v>751.3079569283076</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7881713330213294</v>
+        <v>0.7513079569283075</v>
       </c>
       <c r="G74" t="n">
-        <v>5.717625981141734</v>
+        <v>6.500068512694943</v>
       </c>
       <c r="H74" t="n">
-        <v>9.024018573654087e-12</v>
+        <v>7.949120737945013e-12</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>1000</v>
       </c>
       <c r="C75" t="n">
-        <v>999.8103074968528</v>
+        <v>1000.379766952949</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4760,16 +4760,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>678.8537663498332</v>
+        <v>664.3908774877552</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6788537663498332</v>
+        <v>0.6643908774877553</v>
       </c>
       <c r="G75" t="n">
-        <v>5.717625981141734</v>
+        <v>6.500068512694943</v>
       </c>
       <c r="H75" t="n">
-        <v>9.024018573654087e-12</v>
+        <v>7.949120737945013e-12</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>1000</v>
       </c>
       <c r="C76" t="n">
-        <v>999.6096068104191</v>
+        <v>999.4867554051032</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4818,16 +4818,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>674.4334264573811</v>
+        <v>726.8566312493564</v>
       </c>
       <c r="F76" t="n">
-        <v>0.674433426457381</v>
+        <v>0.7268566312493564</v>
       </c>
       <c r="G76" t="n">
-        <v>6.742468529735442</v>
+        <v>6.140550995847136</v>
       </c>
       <c r="H76" t="n">
-        <v>7.377331772849361e-12</v>
+        <v>8.078221089456365e-12</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>1000</v>
       </c>
       <c r="C77" t="n">
-        <v>999.6096068104191</v>
+        <v>999.4867554051032</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4876,16 +4876,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>624.5140734161748</v>
+        <v>647.53676679758</v>
       </c>
       <c r="F77" t="n">
-        <v>0.6245140734161748</v>
+        <v>0.64753676679758</v>
       </c>
       <c r="G77" t="n">
-        <v>6.742468529735442</v>
+        <v>6.140550995847136</v>
       </c>
       <c r="H77" t="n">
-        <v>7.377331772849361e-12</v>
+        <v>8.078221089456365e-12</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>1000</v>
       </c>
       <c r="C78" t="n">
-        <v>999.8189682196396</v>
+        <v>999.6086029466525</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4934,16 +4934,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>717.3691154281793</v>
+        <v>753.7130667309084</v>
       </c>
       <c r="F78" t="n">
-        <v>0.7173691154281793</v>
+        <v>0.7537130667309084</v>
       </c>
       <c r="G78" t="n">
-        <v>6.4819977374679</v>
+        <v>6.083938076582132</v>
       </c>
       <c r="H78" t="n">
-        <v>7.960207158804579e-12</v>
+        <v>8.375399558160418e-12</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>1000</v>
       </c>
       <c r="C79" t="n">
-        <v>999.8189682196396</v>
+        <v>999.6086029466525</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4992,16 +4992,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>661.5141777800961</v>
+        <v>678.3577912613271</v>
       </c>
       <c r="F79" t="n">
-        <v>0.6615141777800961</v>
+        <v>0.6783577912613271</v>
       </c>
       <c r="G79" t="n">
-        <v>6.4819977374679</v>
+        <v>6.083938076582132</v>
       </c>
       <c r="H79" t="n">
-        <v>7.960207158804579e-12</v>
+        <v>8.375399558160418e-12</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>1000</v>
       </c>
       <c r="C80" t="n">
-        <v>1000.174887811388</v>
+        <v>999.7714067115309</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5050,16 +5050,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>705.0530137837277</v>
+        <v>628.935578140948</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7050530137837276</v>
+        <v>0.628935578140948</v>
       </c>
       <c r="G80" t="n">
-        <v>6.479986908460059</v>
+        <v>7.209959078691926</v>
       </c>
       <c r="H80" t="n">
-        <v>8.037763230113231e-12</v>
+        <v>7.233095249918866e-12</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>1000</v>
       </c>
       <c r="C81" t="n">
-        <v>1000.174887811388</v>
+        <v>999.7714067115309</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5108,16 +5108,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>623.6465414280789</v>
+        <v>591.8510941938446</v>
       </c>
       <c r="F81" t="n">
-        <v>0.6236465414280788</v>
+        <v>0.5918510941938446</v>
       </c>
       <c r="G81" t="n">
-        <v>6.479986908460059</v>
+        <v>7.209959078691926</v>
       </c>
       <c r="H81" t="n">
-        <v>8.037763230113231e-12</v>
+        <v>7.233095249918866e-12</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>1000</v>
       </c>
       <c r="C82" t="n">
-        <v>999.8554704393141</v>
+        <v>1000.201272510234</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5166,16 +5166,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>795.2812929642499</v>
+        <v>849.393993294038</v>
       </c>
       <c r="F82" t="n">
-        <v>0.7952812929642499</v>
+        <v>0.849393993294038</v>
       </c>
       <c r="G82" t="n">
-        <v>5.212419489697575</v>
+        <v>5.439649807613282</v>
       </c>
       <c r="H82" t="n">
-        <v>1.246433283470608e-11</v>
+        <v>1.236043243430013e-11</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>1000</v>
       </c>
       <c r="C83" t="n">
-        <v>999.8554704393141</v>
+        <v>1000.201272510234</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5224,16 +5224,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>732.8179506501369</v>
+        <v>752.5496277563325</v>
       </c>
       <c r="F83" t="n">
-        <v>0.7328179506501369</v>
+        <v>0.7525496277563325</v>
       </c>
       <c r="G83" t="n">
-        <v>5.212419489697575</v>
+        <v>5.439649807613282</v>
       </c>
       <c r="H83" t="n">
-        <v>1.246433283470608e-11</v>
+        <v>1.236043243430013e-11</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>1000</v>
       </c>
       <c r="C84" t="n">
-        <v>999.98659945215</v>
+        <v>999.9556552869635</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5282,16 +5282,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>834.9452943926664</v>
+        <v>843.1813029324265</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8349452943926664</v>
+        <v>0.8431813029324265</v>
       </c>
       <c r="G84" t="n">
-        <v>5.230428349584359</v>
+        <v>5.457072909707055</v>
       </c>
       <c r="H84" t="n">
-        <v>1.211827287443806e-11</v>
+        <v>1.203060189855651e-11</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>1000</v>
       </c>
       <c r="C85" t="n">
-        <v>999.98659945215</v>
+        <v>999.9556552869635</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5340,16 +5340,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>766.164169071089</v>
+        <v>697.5840361877108</v>
       </c>
       <c r="F85" t="n">
-        <v>0.766164169071089</v>
+        <v>0.6975840361877108</v>
       </c>
       <c r="G85" t="n">
-        <v>5.230428349584359</v>
+        <v>5.457072909707055</v>
       </c>
       <c r="H85" t="n">
-        <v>1.211827287443806e-11</v>
+        <v>1.203060189855651e-11</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>1000</v>
       </c>
       <c r="C86" t="n">
-        <v>1000.398685822023</v>
+        <v>1000.118703787651</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5398,16 +5398,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>799.2502920255887</v>
+        <v>801.04797547317</v>
       </c>
       <c r="F86" t="n">
-        <v>0.7992502920255887</v>
+        <v>0.8010479754731701</v>
       </c>
       <c r="G86" t="n">
-        <v>5.313574223717023</v>
+        <v>5.339909966545417</v>
       </c>
       <c r="H86" t="n">
-        <v>1.233079580683628e-11</v>
+        <v>1.202827550341952e-11</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>1000</v>
       </c>
       <c r="C87" t="n">
-        <v>1000.398685822023</v>
+        <v>1000.118703787651</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5456,16 +5456,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>723.6348201400989</v>
+        <v>731.4876632781892</v>
       </c>
       <c r="F87" t="n">
-        <v>0.7236348201400989</v>
+        <v>0.7314876632781891</v>
       </c>
       <c r="G87" t="n">
-        <v>5.313574223717023</v>
+        <v>5.339909966545417</v>
       </c>
       <c r="H87" t="n">
-        <v>1.233079580683628e-11</v>
+        <v>1.202827550341952e-11</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>1000</v>
       </c>
       <c r="C88" t="n">
-        <v>999.8548969901584</v>
+        <v>999.745917769565</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5514,16 +5514,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>804.1815448212785</v>
+        <v>933.7181025805112</v>
       </c>
       <c r="F88" t="n">
-        <v>0.8041815448212786</v>
+        <v>0.9337181025805111</v>
       </c>
       <c r="G88" t="n">
-        <v>5.364761047700855</v>
+        <v>5.309599781216096</v>
       </c>
       <c r="H88" t="n">
-        <v>1.234021325500658e-11</v>
+        <v>1.243797704207535e-11</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>1000</v>
       </c>
       <c r="C89" t="n">
-        <v>999.8548969901584</v>
+        <v>999.745917769565</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5572,16 +5572,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>728.7753765433658</v>
+        <v>806.9821507305643</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7287753765433659</v>
+        <v>0.8069821507305643</v>
       </c>
       <c r="G89" t="n">
-        <v>5.364761047700855</v>
+        <v>5.309599781216096</v>
       </c>
       <c r="H89" t="n">
-        <v>1.234021325500658e-11</v>
+        <v>1.243797704207535e-11</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>1000</v>
       </c>
       <c r="C90" t="n">
-        <v>999.9588582315896</v>
+        <v>999.8985066965104</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5630,16 +5630,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>855.4722092291739</v>
+        <v>903.7994016046748</v>
       </c>
       <c r="F90" t="n">
-        <v>0.8554722092291739</v>
+        <v>0.9037994016046748</v>
       </c>
       <c r="G90" t="n">
-        <v>5.027857806025171</v>
+        <v>5.162667237394648</v>
       </c>
       <c r="H90" t="n">
-        <v>1.283178517210374e-11</v>
+        <v>1.288179805886647e-11</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>1000</v>
       </c>
       <c r="C91" t="n">
-        <v>999.9588582315896</v>
+        <v>999.8985066965104</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>729.6225917098047</v>
+        <v>807.3666898957204</v>
       </c>
       <c r="F91" t="n">
-        <v>0.7296225917098047</v>
+        <v>0.8073666898957204</v>
       </c>
       <c r="G91" t="n">
-        <v>5.027857806025171</v>
+        <v>5.162667237394648</v>
       </c>
       <c r="H91" t="n">
-        <v>1.283178517210374e-11</v>
+        <v>1.288179805886647e-11</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>1000</v>
       </c>
       <c r="C92" t="n">
-        <v>1000.146017626041</v>
+        <v>999.8244582526409</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>825.6054776369531</v>
+        <v>867.1529051480692</v>
       </c>
       <c r="F92" t="n">
-        <v>0.8256054776369531</v>
+        <v>0.8671529051480692</v>
       </c>
       <c r="G92" t="n">
-        <v>5.554236681080777</v>
+        <v>4.724726676949942</v>
       </c>
       <c r="H92" t="n">
-        <v>1.151675237041608e-11</v>
+        <v>1.36754854254369e-11</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>1000</v>
       </c>
       <c r="C93" t="n">
-        <v>1000.146017626041</v>
+        <v>999.8244582526409</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -5804,16 +5804,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>759.1581179369977</v>
+        <v>797.201124327312</v>
       </c>
       <c r="F93" t="n">
-        <v>0.7591581179369976</v>
+        <v>0.7972011243273119</v>
       </c>
       <c r="G93" t="n">
-        <v>5.554236681080777</v>
+        <v>4.724726676949942</v>
       </c>
       <c r="H93" t="n">
-        <v>1.151675237041608e-11</v>
+        <v>1.36754854254369e-11</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>1000</v>
       </c>
       <c r="C94" t="n">
-        <v>1000.151708802448</v>
+        <v>999.908021389694</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5862,16 +5862,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>822.823185871487</v>
+        <v>810.3032676343277</v>
       </c>
       <c r="F94" t="n">
-        <v>0.822823185871487</v>
+        <v>0.8103032676343277</v>
       </c>
       <c r="G94" t="n">
-        <v>5.314768150454423</v>
+        <v>5.154714923994578</v>
       </c>
       <c r="H94" t="n">
-        <v>1.221362989281681e-11</v>
+        <v>1.297703137573468e-11</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>1000</v>
       </c>
       <c r="C95" t="n">
-        <v>1000.151708802448</v>
+        <v>999.908021389694</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5920,16 +5920,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>750.5581248452355</v>
+        <v>734.2010456155383</v>
       </c>
       <c r="F95" t="n">
-        <v>0.7505581248452355</v>
+        <v>0.7342010456155383</v>
       </c>
       <c r="G95" t="n">
-        <v>5.314768150454423</v>
+        <v>5.154714923994578</v>
       </c>
       <c r="H95" t="n">
-        <v>1.221362989281681e-11</v>
+        <v>1.297703137573468e-11</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>1000</v>
       </c>
       <c r="C96" t="n">
-        <v>1000.467194108247</v>
+        <v>999.8234212919947</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5978,16 +5978,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>806.0371908087665</v>
+        <v>783.2083972057357</v>
       </c>
       <c r="F96" t="n">
-        <v>0.8060371908087665</v>
+        <v>0.7832083972057357</v>
       </c>
       <c r="G96" t="n">
-        <v>5.005220130495246</v>
+        <v>5.234717042225499</v>
       </c>
       <c r="H96" t="n">
-        <v>1.269707881248416e-11</v>
+        <v>1.194836079688014e-11</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>1000</v>
       </c>
       <c r="C97" t="n">
-        <v>1000.467194108247</v>
+        <v>999.8234212919947</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6036,16 +6036,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>748.2561596786801</v>
+        <v>702.3779426025262</v>
       </c>
       <c r="F97" t="n">
-        <v>0.7482561596786801</v>
+        <v>0.7023779426025262</v>
       </c>
       <c r="G97" t="n">
-        <v>5.005220130495246</v>
+        <v>5.234717042225499</v>
       </c>
       <c r="H97" t="n">
-        <v>1.269707881248416e-11</v>
+        <v>1.194836079688014e-11</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>1000</v>
       </c>
       <c r="C98" t="n">
-        <v>1000.275997102804</v>
+        <v>1000.160759782844</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6094,16 +6094,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>835.3244284880726</v>
+        <v>821.3261682741258</v>
       </c>
       <c r="F98" t="n">
-        <v>0.8353244284880726</v>
+        <v>0.8213261682741259</v>
       </c>
       <c r="G98" t="n">
-        <v>5.51104630867021</v>
+        <v>5.414674753511311</v>
       </c>
       <c r="H98" t="n">
-        <v>1.155258416214319e-11</v>
+        <v>1.232375726442032e-11</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>1000</v>
       </c>
       <c r="C99" t="n">
-        <v>1000.275997102804</v>
+        <v>1000.160759782844</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6152,16 +6152,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>771.959903511111</v>
+        <v>736.1748677391674</v>
       </c>
       <c r="F99" t="n">
-        <v>0.771959903511111</v>
+        <v>0.7361748677391674</v>
       </c>
       <c r="G99" t="n">
-        <v>5.51104630867021</v>
+        <v>5.414674753511311</v>
       </c>
       <c r="H99" t="n">
-        <v>1.155258416214319e-11</v>
+        <v>1.232375726442032e-11</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>1000</v>
       </c>
       <c r="C100" t="n">
-        <v>999.9604090147537</v>
+        <v>999.6414793837304</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6210,16 +6210,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>779.9357229698034</v>
+        <v>852.9518677891259</v>
       </c>
       <c r="F100" t="n">
-        <v>0.7799357229698034</v>
+        <v>0.8529518677891259</v>
       </c>
       <c r="G100" t="n">
-        <v>5.357755822154898</v>
+        <v>4.985868112506305</v>
       </c>
       <c r="H100" t="n">
-        <v>1.235623548970277e-11</v>
+        <v>1.291806803466822e-11</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>1000</v>
       </c>
       <c r="C101" t="n">
-        <v>999.9604090147537</v>
+        <v>999.6414793837304</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,16 +6268,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>695.9353625269466</v>
+        <v>769.7441014942817</v>
       </c>
       <c r="F101" t="n">
-        <v>0.6959353625269467</v>
+        <v>0.7697441014942817</v>
       </c>
       <c r="G101" t="n">
-        <v>5.357755822154898</v>
+        <v>4.985868112506305</v>
       </c>
       <c r="H101" t="n">
-        <v>1.235623548970277e-11</v>
+        <v>1.291806803466822e-11</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>5000</v>
       </c>
       <c r="C102" t="n">
-        <v>4996.171919477481</v>
+        <v>4994.513049985695</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6326,16 +6326,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>738.5981531077277</v>
+        <v>718.2975672144507</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1477196306215456</v>
+        <v>0.1436595134428902</v>
       </c>
       <c r="G102" t="n">
-        <v>123.468252912907</v>
+        <v>128.0750665149645</v>
       </c>
       <c r="H102" t="n">
-        <v>8.205939971766297e-16</v>
+        <v>8.206960120336744e-16</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>5000</v>
       </c>
       <c r="C103" t="n">
-        <v>4996.171919477481</v>
+        <v>4994.513049985695</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6384,16 +6384,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>672.3008750785996</v>
+        <v>645.9904065251538</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1344601750157199</v>
+        <v>0.1291980813050308</v>
       </c>
       <c r="G103" t="n">
-        <v>123.468252912907</v>
+        <v>128.0750665149645</v>
       </c>
       <c r="H103" t="n">
-        <v>8.205939971766297e-16</v>
+        <v>8.206960120336744e-16</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>5000</v>
       </c>
       <c r="C104" t="n">
-        <v>4999.02194270166</v>
+        <v>4997.076482232464</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6442,16 +6442,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>735.3439674398107</v>
+        <v>772.4464213838776</v>
       </c>
       <c r="F104" t="n">
-        <v>0.1470687934879621</v>
+        <v>0.1544892842767755</v>
       </c>
       <c r="G104" t="n">
-        <v>120.6726469820478</v>
+        <v>100.276111557596</v>
       </c>
       <c r="H104" t="n">
-        <v>8.356744981864441e-16</v>
+        <v>6.114983587077133e-16</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>5000</v>
       </c>
       <c r="C105" t="n">
-        <v>4999.02194270166</v>
+        <v>4997.076482232464</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6500,16 +6500,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>663.620681646152</v>
+        <v>695.7157287436277</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1327241363292304</v>
+        <v>0.1391431457487255</v>
       </c>
       <c r="G105" t="n">
-        <v>120.6726469820478</v>
+        <v>100.276111557596</v>
       </c>
       <c r="H105" t="n">
-        <v>8.356744981864441e-16</v>
+        <v>6.114983587077133e-16</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>5000</v>
       </c>
       <c r="C106" t="n">
-        <v>5000.153172260392</v>
+        <v>4999.401167701174</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6558,16 +6558,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>809.3616032898065</v>
+        <v>765.1440464720046</v>
       </c>
       <c r="F106" t="n">
-        <v>0.1618723206579613</v>
+        <v>0.1530288092944009</v>
       </c>
       <c r="G106" t="n">
-        <v>88.10111455832104</v>
+        <v>106.4012119461766</v>
       </c>
       <c r="H106" t="n">
-        <v>5.421585647109697e-16</v>
+        <v>6.805799758348728e-16</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>5000</v>
       </c>
       <c r="C107" t="n">
-        <v>5000.153172260392</v>
+        <v>4999.401167701174</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6616,16 +6616,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>735.113957445653</v>
+        <v>693.0025818652865</v>
       </c>
       <c r="F107" t="n">
-        <v>0.1470227914891306</v>
+        <v>0.1386005163730573</v>
       </c>
       <c r="G107" t="n">
-        <v>88.10111455832104</v>
+        <v>106.4012119461766</v>
       </c>
       <c r="H107" t="n">
-        <v>5.421585647109697e-16</v>
+        <v>6.805799758348728e-16</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>5000</v>
       </c>
       <c r="C108" t="n">
-        <v>4995.758974065116</v>
+        <v>4998.283546894271</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6674,16 +6674,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>741.418683694332</v>
+        <v>732.3980146216244</v>
       </c>
       <c r="F108" t="n">
-        <v>0.1482837367388664</v>
+        <v>0.1464796029243249</v>
       </c>
       <c r="G108" t="n">
-        <v>120.0922239516942</v>
+        <v>117.6741138541797</v>
       </c>
       <c r="H108" t="n">
-        <v>8.327518169783678e-16</v>
+        <v>7.748091598178508e-16</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>5000</v>
       </c>
       <c r="C109" t="n">
-        <v>4995.758974065116</v>
+        <v>4998.283546894271</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -6732,16 +6732,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>668.5301129184018</v>
+        <v>662.8092069692086</v>
       </c>
       <c r="F109" t="n">
-        <v>0.1337060225836804</v>
+        <v>0.1325618413938417</v>
       </c>
       <c r="G109" t="n">
-        <v>120.0922239516942</v>
+        <v>117.6741138541797</v>
       </c>
       <c r="H109" t="n">
-        <v>8.327518169783678e-16</v>
+        <v>7.748091598178508e-16</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>5000</v>
       </c>
       <c r="C110" t="n">
-        <v>4996.488797797816</v>
+        <v>4996.940810743074</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6790,16 +6790,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>716.3119631902777</v>
+        <v>731.044391219657</v>
       </c>
       <c r="F110" t="n">
-        <v>0.1432623926380555</v>
+        <v>0.1462088782439314</v>
       </c>
       <c r="G110" t="n">
-        <v>128.2128941924195</v>
+        <v>125.8135716750275</v>
       </c>
       <c r="H110" t="n">
-        <v>8.101754294891044e-16</v>
+        <v>8.250768976256317e-16</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>5000</v>
       </c>
       <c r="C111" t="n">
-        <v>4996.488797797816</v>
+        <v>4996.940810743074</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -6848,16 +6848,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>646.9865513552694</v>
+        <v>662.2233246494928</v>
       </c>
       <c r="F111" t="n">
-        <v>0.1293973102710539</v>
+        <v>0.1324446649298986</v>
       </c>
       <c r="G111" t="n">
-        <v>128.2128941924195</v>
+        <v>125.8135716750275</v>
       </c>
       <c r="H111" t="n">
-        <v>8.101754294891044e-16</v>
+        <v>8.250768976256317e-16</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>5000</v>
       </c>
       <c r="C112" t="n">
-        <v>4995.272565847804</v>
+        <v>4997.176994687247</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -6906,16 +6906,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>742.7342237704785</v>
+        <v>806.2489420371627</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1485468447540957</v>
+        <v>0.1612497884074325</v>
       </c>
       <c r="G112" t="n">
-        <v>122.1558808932696</v>
+        <v>87.06769158817933</v>
       </c>
       <c r="H112" t="n">
-        <v>8.257298343968934e-16</v>
+        <v>5.262731968200486e-16</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>5000</v>
       </c>
       <c r="C113" t="n">
-        <v>4995.272565847804</v>
+        <v>4997.176994687247</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -6964,16 +6964,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>670.4830230122636</v>
+        <v>734.1437844369808</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1340966046024527</v>
+        <v>0.1468287568873962</v>
       </c>
       <c r="G113" t="n">
-        <v>122.1558808932696</v>
+        <v>87.06769158817933</v>
       </c>
       <c r="H113" t="n">
-        <v>8.257298343968934e-16</v>
+        <v>5.262731968200486e-16</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>5000</v>
       </c>
       <c r="C114" t="n">
-        <v>4997.430626693409</v>
+        <v>4996.801377889044</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7022,16 +7022,16 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>737.8216452890658</v>
+        <v>728.5845784485846</v>
       </c>
       <c r="F114" t="n">
-        <v>0.1475643290578132</v>
+        <v>0.1457169156897169</v>
       </c>
       <c r="G114" t="n">
-        <v>120.2131015017274</v>
+        <v>121.1964039887153</v>
       </c>
       <c r="H114" t="n">
-        <v>7.496788763524985e-16</v>
+        <v>8.001190780865557e-16</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>5000</v>
       </c>
       <c r="C115" t="n">
-        <v>4997.430626693409</v>
+        <v>4996.801377889044</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7080,16 +7080,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>669.2859617292855</v>
+        <v>656.0932316493825</v>
       </c>
       <c r="F115" t="n">
-        <v>0.1338571923458571</v>
+        <v>0.1312186463298765</v>
       </c>
       <c r="G115" t="n">
-        <v>120.2131015017274</v>
+        <v>121.1964039887153</v>
       </c>
       <c r="H115" t="n">
-        <v>7.496788763524985e-16</v>
+        <v>8.001190780865557e-16</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>5000</v>
       </c>
       <c r="C116" t="n">
-        <v>4997.907890674811</v>
+        <v>5000.508819895861</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7138,16 +7138,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>797.078138628392</v>
+        <v>782.8841366687246</v>
       </c>
       <c r="F116" t="n">
-        <v>0.1594156277256784</v>
+        <v>0.1565768273337449</v>
       </c>
       <c r="G116" t="n">
-        <v>89.19629250319562</v>
+        <v>92.0148366301262</v>
       </c>
       <c r="H116" t="n">
-        <v>4.933475580806425e-16</v>
+        <v>5.358795228080091e-16</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>5000</v>
       </c>
       <c r="C117" t="n">
-        <v>4997.907890674811</v>
+        <v>5000.508819895861</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7196,16 +7196,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>722.7536387925608</v>
+        <v>719.7389934456343</v>
       </c>
       <c r="F117" t="n">
-        <v>0.1445507277585122</v>
+        <v>0.1439477986891269</v>
       </c>
       <c r="G117" t="n">
-        <v>89.19629250319562</v>
+        <v>92.0148366301262</v>
       </c>
       <c r="H117" t="n">
-        <v>4.933475580806425e-16</v>
+        <v>5.358795228080091e-16</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>5000</v>
       </c>
       <c r="C118" t="n">
-        <v>5001.498539936022</v>
+        <v>4997.431759686296</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7254,16 +7254,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>728.3395760231597</v>
+        <v>759.2987545566714</v>
       </c>
       <c r="F118" t="n">
-        <v>0.1456679152046319</v>
+        <v>0.1518597509113343</v>
       </c>
       <c r="G118" t="n">
-        <v>126.486326177142</v>
+        <v>112.8518072363952</v>
       </c>
       <c r="H118" t="n">
-        <v>8.154980973558238e-16</v>
+        <v>6.967264961753288e-16</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>5000</v>
       </c>
       <c r="C119" t="n">
-        <v>5001.498539936022</v>
+        <v>4997.431759686296</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7312,16 +7312,16 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>662.6681807720439</v>
+        <v>681.0178679159526</v>
       </c>
       <c r="F119" t="n">
-        <v>0.1325336361544088</v>
+        <v>0.1362035735831905</v>
       </c>
       <c r="G119" t="n">
-        <v>126.486326177142</v>
+        <v>112.8518072363952</v>
       </c>
       <c r="H119" t="n">
-        <v>8.154980973558238e-16</v>
+        <v>6.967264961753288e-16</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>5000</v>
       </c>
       <c r="C120" t="n">
-        <v>4998.760978876405</v>
+        <v>5001.684199383935</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7370,16 +7370,16 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>728.4122434009669</v>
+        <v>810.2473228614274</v>
       </c>
       <c r="F120" t="n">
-        <v>0.1456824486801934</v>
+        <v>0.1620494645722855</v>
       </c>
       <c r="G120" t="n">
-        <v>123.6411067776428</v>
+        <v>87.13466729765402</v>
       </c>
       <c r="H120" t="n">
-        <v>8.046131542976861e-16</v>
+        <v>5.737085982326729e-16</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>5000</v>
       </c>
       <c r="C121" t="n">
-        <v>4998.760978876405</v>
+        <v>5001.684199383935</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7428,16 +7428,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>656.2942352198822</v>
+        <v>735.7343104942069</v>
       </c>
       <c r="F121" t="n">
-        <v>0.1312588470439764</v>
+        <v>0.1471468620988414</v>
       </c>
       <c r="G121" t="n">
-        <v>123.6411067776428</v>
+        <v>87.13466729765402</v>
       </c>
       <c r="H121" t="n">
-        <v>8.046131542976861e-16</v>
+        <v>5.737085982326729e-16</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>5000</v>
       </c>
       <c r="C122" t="n">
-        <v>4998.803869552033</v>
+        <v>5000.91498249778</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7486,16 +7486,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1091.985672418748</v>
+        <v>1042.691966613203</v>
       </c>
       <c r="F122" t="n">
-        <v>0.2183971344837496</v>
+        <v>0.2085383933226405</v>
       </c>
       <c r="G122" t="n">
-        <v>58.89322617886465</v>
+        <v>60.72922932250226</v>
       </c>
       <c r="H122" t="n">
-        <v>3.201880658195189e-15</v>
+        <v>3.189347637672279e-15</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>5000</v>
       </c>
       <c r="C123" t="n">
-        <v>4998.803869552033</v>
+        <v>5000.91498249778</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7544,16 +7544,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>977.1556544758519</v>
+        <v>939.7765951153564</v>
       </c>
       <c r="F123" t="n">
-        <v>0.1954311308951704</v>
+        <v>0.1879553190230713</v>
       </c>
       <c r="G123" t="n">
-        <v>58.89322617886465</v>
+        <v>60.72922932250226</v>
       </c>
       <c r="H123" t="n">
-        <v>3.201880658195189e-15</v>
+        <v>3.189347637672279e-15</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>5000</v>
       </c>
       <c r="C124" t="n">
-        <v>4998.636728553475</v>
+        <v>5000.680401362976</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7602,16 +7602,16 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1058.429062925706</v>
+        <v>1041.737474670453</v>
       </c>
       <c r="F124" t="n">
-        <v>0.2116858125851412</v>
+        <v>0.2083474949340905</v>
       </c>
       <c r="G124" t="n">
-        <v>60.31579541425563</v>
+        <v>59.2098260467824</v>
       </c>
       <c r="H124" t="n">
-        <v>3.089702576509259e-15</v>
+        <v>3.273747836206113e-15</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>5000</v>
       </c>
       <c r="C125" t="n">
-        <v>4998.636728553475</v>
+        <v>5000.680401362976</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7660,16 +7660,16 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>952.0350486129043</v>
+        <v>952.1215944525433</v>
       </c>
       <c r="F125" t="n">
-        <v>0.1904070097225809</v>
+        <v>0.1904243188905086</v>
       </c>
       <c r="G125" t="n">
-        <v>60.31579541425563</v>
+        <v>59.2098260467824</v>
       </c>
       <c r="H125" t="n">
-        <v>3.089702576509259e-15</v>
+        <v>3.273747836206113e-15</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>5000</v>
       </c>
       <c r="C126" t="n">
-        <v>4999.295040780218</v>
+        <v>4999.389205191829</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -7718,16 +7718,16 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1042.435863418752</v>
+        <v>1046.850400782535</v>
       </c>
       <c r="F126" t="n">
-        <v>0.2084871726837504</v>
+        <v>0.209370080156507</v>
       </c>
       <c r="G126" t="n">
-        <v>59.6813383437538</v>
+        <v>62.72436275243069</v>
       </c>
       <c r="H126" t="n">
-        <v>3.144774936918949e-15</v>
+        <v>3.318805861581349e-15</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>5000</v>
       </c>
       <c r="C127" t="n">
-        <v>4999.295040780218</v>
+        <v>4999.389205191829</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -7776,16 +7776,16 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>943.6913661384121</v>
+        <v>943.7038253264519</v>
       </c>
       <c r="F127" t="n">
-        <v>0.1887382732276824</v>
+        <v>0.1887407650652904</v>
       </c>
       <c r="G127" t="n">
-        <v>59.6813383437538</v>
+        <v>62.72436275243069</v>
       </c>
       <c r="H127" t="n">
-        <v>3.144774936918949e-15</v>
+        <v>3.318805861581349e-15</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>5000</v>
       </c>
       <c r="C128" t="n">
-        <v>4999.230415570176</v>
+        <v>4999.523596438055</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -7834,16 +7834,16 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1046.669948557795</v>
+        <v>1060.476410921514</v>
       </c>
       <c r="F128" t="n">
-        <v>0.2093339897115591</v>
+        <v>0.2120952821843028</v>
       </c>
       <c r="G128" t="n">
-        <v>63.44632822601994</v>
+        <v>60.58295376981127</v>
       </c>
       <c r="H128" t="n">
-        <v>3.276508703648492e-15</v>
+        <v>3.380797049921725e-15</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>5000</v>
       </c>
       <c r="C129" t="n">
-        <v>4999.230415570176</v>
+        <v>4999.523596438055</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -7892,16 +7892,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>934.9781675892312</v>
+        <v>950.46590947787</v>
       </c>
       <c r="F129" t="n">
-        <v>0.1869956335178463</v>
+        <v>0.190093181895574</v>
       </c>
       <c r="G129" t="n">
-        <v>63.44632822601994</v>
+        <v>60.58295376981127</v>
       </c>
       <c r="H129" t="n">
-        <v>3.276508703648492e-15</v>
+        <v>3.380797049921725e-15</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>5000</v>
       </c>
       <c r="C130" t="n">
-        <v>4997.617669732735</v>
+        <v>4998.625077046848</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -7950,16 +7950,16 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1061.772229934854</v>
+        <v>1067.012703240832</v>
       </c>
       <c r="F130" t="n">
-        <v>0.2123544459869708</v>
+        <v>0.2134025406481665</v>
       </c>
       <c r="G130" t="n">
-        <v>60.25401314048743</v>
+        <v>61.62167177303709</v>
       </c>
       <c r="H130" t="n">
-        <v>3.367520094163209e-15</v>
+        <v>3.307933027634222e-15</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>5000</v>
       </c>
       <c r="C131" t="n">
-        <v>4997.617669732735</v>
+        <v>4998.625077046848</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8008,16 +8008,16 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>948.0219235740781</v>
+        <v>967.9043251787026</v>
       </c>
       <c r="F131" t="n">
-        <v>0.1896043847148156</v>
+        <v>0.1935808650357405</v>
       </c>
       <c r="G131" t="n">
-        <v>60.25401314048743</v>
+        <v>61.62167177303709</v>
       </c>
       <c r="H131" t="n">
-        <v>3.367520094163209e-15</v>
+        <v>3.307933027634222e-15</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>5000</v>
       </c>
       <c r="C132" t="n">
-        <v>4999.309162695869</v>
+        <v>4998.534064788502</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8066,16 +8066,16 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1077.538277034767</v>
+        <v>1022.239540805302</v>
       </c>
       <c r="F132" t="n">
-        <v>0.2155076554069534</v>
+        <v>0.2044479081610605</v>
       </c>
       <c r="G132" t="n">
-        <v>56.50153993251157</v>
+        <v>63.42780222276204</v>
       </c>
       <c r="H132" t="n">
-        <v>3.155665752809518e-15</v>
+        <v>3.23315971694202e-15</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>5000</v>
       </c>
       <c r="C133" t="n">
-        <v>4999.309162695869</v>
+        <v>4998.534064788502</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8124,16 +8124,16 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>980.5632469870872</v>
+        <v>936.7437378064286</v>
       </c>
       <c r="F133" t="n">
-        <v>0.1961126493974174</v>
+        <v>0.1873487475612857</v>
       </c>
       <c r="G133" t="n">
-        <v>56.50153993251157</v>
+        <v>63.42780222276204</v>
       </c>
       <c r="H133" t="n">
-        <v>3.155665752809518e-15</v>
+        <v>3.23315971694202e-15</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>5000</v>
       </c>
       <c r="C134" t="n">
-        <v>4998.358654533731</v>
+        <v>4998.751575133117</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8182,16 +8182,16 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1050.542726448414</v>
+        <v>1066.850175426364</v>
       </c>
       <c r="F134" t="n">
-        <v>0.2101085452896829</v>
+        <v>0.2133700350852728</v>
       </c>
       <c r="G134" t="n">
-        <v>61.25214600776027</v>
+        <v>60.47070342705909</v>
       </c>
       <c r="H134" t="n">
-        <v>3.216383045291273e-15</v>
+        <v>3.254378060589122e-15</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>5000</v>
       </c>
       <c r="C135" t="n">
-        <v>4998.358654533731</v>
+        <v>4998.751575133117</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8240,16 +8240,16 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>952.535705001502</v>
+        <v>958.0392564113532</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1905071410003004</v>
+        <v>0.1916078512822706</v>
       </c>
       <c r="G135" t="n">
-        <v>61.25214600776027</v>
+        <v>60.47070342705909</v>
       </c>
       <c r="H135" t="n">
-        <v>3.216383045291273e-15</v>
+        <v>3.254378060589122e-15</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>5000</v>
       </c>
       <c r="C136" t="n">
-        <v>5000.274661382944</v>
+        <v>4999.775733274309</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8298,16 +8298,16 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1043.2631675209</v>
+        <v>1048.089186165984</v>
       </c>
       <c r="F136" t="n">
-        <v>0.2086526335041799</v>
+        <v>0.2096178372331968</v>
       </c>
       <c r="G136" t="n">
-        <v>62.04195062353458</v>
+        <v>61.9392718137308</v>
       </c>
       <c r="H136" t="n">
-        <v>3.335954684902711e-15</v>
+        <v>3.301348956662903e-15</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>5000</v>
       </c>
       <c r="C137" t="n">
-        <v>5000.274661382944</v>
+        <v>4999.775733274309</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8356,16 +8356,16 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>934.129140433923</v>
+        <v>936.0274523132205</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1868258280867846</v>
+        <v>0.1872054904626441</v>
       </c>
       <c r="G137" t="n">
-        <v>62.04195062353458</v>
+        <v>61.9392718137308</v>
       </c>
       <c r="H137" t="n">
-        <v>3.335954684902711e-15</v>
+        <v>3.301348956662903e-15</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>5000</v>
       </c>
       <c r="C138" t="n">
-        <v>5000.747201560668</v>
+        <v>4998.564018669901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8414,16 +8414,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1061.209381591326</v>
+        <v>1076.646090959885</v>
       </c>
       <c r="F138" t="n">
-        <v>0.2122418763182651</v>
+        <v>0.2153292181919769</v>
       </c>
       <c r="G138" t="n">
-        <v>57.51232640602205</v>
+        <v>58.62986010631724</v>
       </c>
       <c r="H138" t="n">
-        <v>3.182748521352473e-15</v>
+        <v>3.175464736372273e-15</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>5000</v>
       </c>
       <c r="C139" t="n">
-        <v>5000.747201560668</v>
+        <v>4998.564018669901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8472,16 +8472,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>963.2315986979276</v>
+        <v>963.595601440789</v>
       </c>
       <c r="F139" t="n">
-        <v>0.1926463197395855</v>
+        <v>0.1927191202881578</v>
       </c>
       <c r="G139" t="n">
-        <v>57.51232640602205</v>
+        <v>58.62986010631724</v>
       </c>
       <c r="H139" t="n">
-        <v>3.182748521352473e-15</v>
+        <v>3.175464736372273e-15</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>5000</v>
       </c>
       <c r="C140" t="n">
-        <v>4998.725184085311</v>
+        <v>5000.13202377083</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8530,16 +8530,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1029.380498845459</v>
+        <v>1036.178200128497</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2058760997690918</v>
+        <v>0.2072356400256994</v>
       </c>
       <c r="G140" t="n">
-        <v>64.17171285455089</v>
+        <v>63.98547465344805</v>
       </c>
       <c r="H140" t="n">
-        <v>3.191405012458971e-15</v>
+        <v>3.252964844759191e-15</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>5000</v>
       </c>
       <c r="C141" t="n">
-        <v>4998.725184085311</v>
+        <v>5000.13202377083</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8588,16 +8588,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>933.8775688250715</v>
+        <v>923.9865518311084</v>
       </c>
       <c r="F141" t="n">
-        <v>0.1867755137650143</v>
+        <v>0.1847973103662217</v>
       </c>
       <c r="G141" t="n">
-        <v>64.17171285455089</v>
+        <v>63.98547465344805</v>
       </c>
       <c r="H141" t="n">
-        <v>3.191405012458971e-15</v>
+        <v>3.252964844759191e-15</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>5000</v>
       </c>
       <c r="C142" t="n">
-        <v>5000.859018785627</v>
+        <v>5000.500208420497</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8646,16 +8646,16 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1280.069800460903</v>
+        <v>1269.405501046353</v>
       </c>
       <c r="F142" t="n">
-        <v>0.2560139600921806</v>
+        <v>0.2538811002092706</v>
       </c>
       <c r="G142" t="n">
-        <v>40.99733484678973</v>
+        <v>41.86227664003446</v>
       </c>
       <c r="H142" t="n">
-        <v>7.314934861228404e-15</v>
+        <v>7.231243980713098e-15</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>5000</v>
       </c>
       <c r="C143" t="n">
-        <v>5000.859018785627</v>
+        <v>5000.500208420497</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -8704,16 +8704,16 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1153.823210758187</v>
+        <v>1161.628919410294</v>
       </c>
       <c r="F143" t="n">
-        <v>0.2307646421516375</v>
+        <v>0.2323257838820589</v>
       </c>
       <c r="G143" t="n">
-        <v>40.99733484678973</v>
+        <v>41.86227664003446</v>
       </c>
       <c r="H143" t="n">
-        <v>7.314934861228404e-15</v>
+        <v>7.231243980713098e-15</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>5000</v>
       </c>
       <c r="C144" t="n">
-        <v>4998.636597579302</v>
+        <v>5000.42633580652</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -8762,16 +8762,16 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1301.784823256822</v>
+        <v>1305.48526932639</v>
       </c>
       <c r="F144" t="n">
-        <v>0.2603569646513643</v>
+        <v>0.2610970538652781</v>
       </c>
       <c r="G144" t="n">
-        <v>38.73074571040915</v>
+        <v>38.77599652192021</v>
       </c>
       <c r="H144" t="n">
-        <v>7.636139326236821e-15</v>
+        <v>7.542804070476285e-15</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>5000</v>
       </c>
       <c r="C145" t="n">
-        <v>4998.636597579302</v>
+        <v>5000.42633580652</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -8820,16 +8820,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1177.858650901619</v>
+        <v>1178.326286351842</v>
       </c>
       <c r="F145" t="n">
-        <v>0.2355717301803238</v>
+        <v>0.2356652572703684</v>
       </c>
       <c r="G145" t="n">
-        <v>38.73074571040915</v>
+        <v>38.77599652192021</v>
       </c>
       <c r="H145" t="n">
-        <v>7.636139326236821e-15</v>
+        <v>7.542804070476285e-15</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>5000</v>
       </c>
       <c r="C146" t="n">
-        <v>4999.315574044296</v>
+        <v>5000.409128536815</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -8878,16 +8878,16 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1249.701799443029</v>
+        <v>1267.014456964821</v>
       </c>
       <c r="F146" t="n">
-        <v>0.2499403598886059</v>
+        <v>0.2534028913929643</v>
       </c>
       <c r="G146" t="n">
-        <v>43.0611409311802</v>
+        <v>42.19115520962016</v>
       </c>
       <c r="H146" t="n">
-        <v>7.256315760587254e-15</v>
+        <v>7.095075713961966e-15</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>5000</v>
       </c>
       <c r="C147" t="n">
-        <v>4999.315574044296</v>
+        <v>5000.409128536815</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -8936,16 +8936,16 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1150.659747402491</v>
+        <v>1157.574985295206</v>
       </c>
       <c r="F147" t="n">
-        <v>0.2301319494804982</v>
+        <v>0.2315149970590413</v>
       </c>
       <c r="G147" t="n">
-        <v>43.0611409311802</v>
+        <v>42.19115520962016</v>
       </c>
       <c r="H147" t="n">
-        <v>7.256315760587254e-15</v>
+        <v>7.095075713961966e-15</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>5000</v>
       </c>
       <c r="C148" t="n">
-        <v>4999.576618102517</v>
+        <v>4999.024679436787</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -8994,16 +8994,16 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1307.549946334532</v>
+        <v>1269.495311919227</v>
       </c>
       <c r="F148" t="n">
-        <v>0.2615099892669065</v>
+        <v>0.2538990623838454</v>
       </c>
       <c r="G148" t="n">
-        <v>40.81144688900642</v>
+        <v>44.15765359944972</v>
       </c>
       <c r="H148" t="n">
-        <v>7.424854089279503e-15</v>
+        <v>7.178043431504454e-15</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>5000</v>
       </c>
       <c r="C149" t="n">
-        <v>4999.576618102517</v>
+        <v>4999.024679436787</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9052,16 +9052,16 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1177.452311697913</v>
+        <v>1140.082194642459</v>
       </c>
       <c r="F149" t="n">
-        <v>0.2354904623395826</v>
+        <v>0.2280164389284918</v>
       </c>
       <c r="G149" t="n">
-        <v>40.81144688900642</v>
+        <v>44.15765359944972</v>
       </c>
       <c r="H149" t="n">
-        <v>7.424854089279503e-15</v>
+        <v>7.178043431504454e-15</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>5000</v>
       </c>
       <c r="C150" t="n">
-        <v>4999.293319504859</v>
+        <v>5000.491211556552</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9110,16 +9110,16 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1294.080548764721</v>
+        <v>1334.848418792787</v>
       </c>
       <c r="F150" t="n">
-        <v>0.2588161097529441</v>
+        <v>0.2669696837585573</v>
       </c>
       <c r="G150" t="n">
-        <v>41.2917516685231</v>
+        <v>37.36189255640917</v>
       </c>
       <c r="H150" t="n">
-        <v>7.505661823997945e-15</v>
+        <v>7.504296754523305e-15</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>5000</v>
       </c>
       <c r="C151" t="n">
-        <v>4999.293319504859</v>
+        <v>5000.491211556552</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9168,16 +9168,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1161.596909688393</v>
+        <v>1208.465989725123</v>
       </c>
       <c r="F151" t="n">
-        <v>0.2323193819376786</v>
+        <v>0.2416931979450246</v>
       </c>
       <c r="G151" t="n">
-        <v>41.2917516685231</v>
+        <v>37.36189255640917</v>
       </c>
       <c r="H151" t="n">
-        <v>7.505661823997945e-15</v>
+        <v>7.504296754523305e-15</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>5000</v>
       </c>
       <c r="C152" t="n">
-        <v>5000.110502641878</v>
+        <v>5000.589799461914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9226,16 +9226,16 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1270.529475265312</v>
+        <v>1289.527183414933</v>
       </c>
       <c r="F152" t="n">
-        <v>0.2541058950530625</v>
+        <v>0.2579054366829866</v>
       </c>
       <c r="G152" t="n">
-        <v>42.35166319789936</v>
+        <v>41.22812094709423</v>
       </c>
       <c r="H152" t="n">
-        <v>7.252271605861994e-15</v>
+        <v>7.414306871374383e-15</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>5000</v>
       </c>
       <c r="C153" t="n">
-        <v>5000.110502641878</v>
+        <v>5000.589799461914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9284,16 +9284,16 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1157.054075015513</v>
+        <v>1164.231895136837</v>
       </c>
       <c r="F153" t="n">
-        <v>0.2314108150031026</v>
+        <v>0.2328463790273673</v>
       </c>
       <c r="G153" t="n">
-        <v>42.35166319789936</v>
+        <v>41.22812094709423</v>
       </c>
       <c r="H153" t="n">
-        <v>7.252271605861994e-15</v>
+        <v>7.414306871374383e-15</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>5000</v>
       </c>
       <c r="C154" t="n">
-        <v>4999.090038550744</v>
+        <v>5000.054719182704</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9342,16 +9342,16 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1274.098867612624</v>
+        <v>1260.958349428784</v>
       </c>
       <c r="F154" t="n">
-        <v>0.2548197735225249</v>
+        <v>0.2521916698857567</v>
       </c>
       <c r="G154" t="n">
-        <v>41.06876114627799</v>
+        <v>42.32157965258247</v>
       </c>
       <c r="H154" t="n">
-        <v>7.437606093688344e-15</v>
+        <v>7.002956324566233e-15</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>5000</v>
       </c>
       <c r="C155" t="n">
-        <v>4999.090038550744</v>
+        <v>5000.054719182704</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9400,16 +9400,16 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1146.41546158994</v>
+        <v>1123.71495112707</v>
       </c>
       <c r="F155" t="n">
-        <v>0.229283092317988</v>
+        <v>0.2247429902254141</v>
       </c>
       <c r="G155" t="n">
-        <v>41.06876114627799</v>
+        <v>42.32157965258247</v>
       </c>
       <c r="H155" t="n">
-        <v>7.437606093688344e-15</v>
+        <v>7.002956324566233e-15</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>5000</v>
       </c>
       <c r="C156" t="n">
-        <v>4999.726081596322</v>
+        <v>5000.014722807139</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9458,16 +9458,16 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1271.953641068745</v>
+        <v>1276.243141789479</v>
       </c>
       <c r="F156" t="n">
-        <v>0.254390728213749</v>
+        <v>0.2552486283578958</v>
       </c>
       <c r="G156" t="n">
-        <v>41.50262347375591</v>
+        <v>40.35777683772003</v>
       </c>
       <c r="H156" t="n">
-        <v>7.430346939025429e-15</v>
+        <v>7.420406760227628e-15</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>5000</v>
       </c>
       <c r="C157" t="n">
-        <v>4999.726081596322</v>
+        <v>5000.014722807139</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9516,16 +9516,16 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1148.517526260446</v>
+        <v>1150.60607868171</v>
       </c>
       <c r="F157" t="n">
-        <v>0.2297035052520893</v>
+        <v>0.2301212157363421</v>
       </c>
       <c r="G157" t="n">
-        <v>41.50262347375591</v>
+        <v>40.35777683772003</v>
       </c>
       <c r="H157" t="n">
-        <v>7.430346939025429e-15</v>
+        <v>7.420406760227628e-15</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>5000</v>
       </c>
       <c r="C158" t="n">
-        <v>4999.217458280339</v>
+        <v>4998.729593577506</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9574,16 +9574,16 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1290.173123226726</v>
+        <v>1298.403272537973</v>
       </c>
       <c r="F158" t="n">
-        <v>0.2580346246453452</v>
+        <v>0.2596806545075946</v>
       </c>
       <c r="G158" t="n">
-        <v>39.7733461920543</v>
+        <v>41.39499448815184</v>
       </c>
       <c r="H158" t="n">
-        <v>7.375303901629947e-15</v>
+        <v>7.324523522231592e-15</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>5000</v>
       </c>
       <c r="C159" t="n">
-        <v>4999.217458280339</v>
+        <v>4998.729593577506</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9632,16 +9632,16 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1161.271440023628</v>
+        <v>1172.802399812156</v>
       </c>
       <c r="F159" t="n">
-        <v>0.2322542880047256</v>
+        <v>0.2345604799624311</v>
       </c>
       <c r="G159" t="n">
-        <v>39.7733461920543</v>
+        <v>41.39499448815184</v>
       </c>
       <c r="H159" t="n">
-        <v>7.375303901629947e-15</v>
+        <v>7.324523522231592e-15</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>5000</v>
       </c>
       <c r="C160" t="n">
-        <v>5001.451835132907</v>
+        <v>4999.689629719695</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -9690,16 +9690,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1279.129495551215</v>
+        <v>1245.168613987973</v>
       </c>
       <c r="F160" t="n">
-        <v>0.2558258991102429</v>
+        <v>0.2490337227975946</v>
       </c>
       <c r="G160" t="n">
-        <v>40.43410750515979</v>
+        <v>43.51980912919334</v>
       </c>
       <c r="H160" t="n">
-        <v>7.348548873570974e-15</v>
+        <v>7.207235081326855e-15</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>5000</v>
       </c>
       <c r="C161" t="n">
-        <v>5001.451835132907</v>
+        <v>4999.689629719695</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -9748,16 +9748,16 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1160.750452315804</v>
+        <v>1122.770794123908</v>
       </c>
       <c r="F161" t="n">
-        <v>0.2321500904631608</v>
+        <v>0.2245541588247815</v>
       </c>
       <c r="G161" t="n">
-        <v>40.43410750515979</v>
+        <v>43.51980912919334</v>
       </c>
       <c r="H161" t="n">
-        <v>7.348548873570974e-15</v>
+        <v>7.207235081326855e-15</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>5000</v>
       </c>
       <c r="C162" t="n">
-        <v>4999.288614198563</v>
+        <v>5000.318944711616</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -9806,16 +9806,16 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1519.742420216265</v>
+        <v>1480.92145629569</v>
       </c>
       <c r="F162" t="n">
-        <v>0.303948484043253</v>
+        <v>0.2961842912591381</v>
       </c>
       <c r="G162" t="n">
-        <v>30.67640345077804</v>
+        <v>30.79495538470294</v>
       </c>
       <c r="H162" t="n">
-        <v>1.326212392520206e-14</v>
+        <v>1.297093004614632e-14</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>5000</v>
       </c>
       <c r="C163" t="n">
-        <v>4999.288614198563</v>
+        <v>5000.318944711616</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -9864,16 +9864,16 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1353.565326253133</v>
+        <v>1318.536604272758</v>
       </c>
       <c r="F163" t="n">
-        <v>0.2707130652506266</v>
+        <v>0.2637073208545517</v>
       </c>
       <c r="G163" t="n">
-        <v>30.67640345077804</v>
+        <v>30.79495538470294</v>
       </c>
       <c r="H163" t="n">
-        <v>1.326212392520206e-14</v>
+        <v>1.297093004614632e-14</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>5000</v>
       </c>
       <c r="C164" t="n">
-        <v>5000.451558068674</v>
+        <v>4999.833584813202</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -9922,16 +9922,16 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1469.893672555238</v>
+        <v>1516.837210279069</v>
       </c>
       <c r="F164" t="n">
-        <v>0.2939787345110476</v>
+        <v>0.3033674420558137</v>
       </c>
       <c r="G164" t="n">
-        <v>31.83591229064437</v>
+        <v>28.2979793567971</v>
       </c>
       <c r="H164" t="n">
-        <v>1.281085642037459e-14</v>
+        <v>1.340171589118595e-14</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>5000</v>
       </c>
       <c r="C165" t="n">
-        <v>5000.451558068674</v>
+        <v>4999.833584813202</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -9980,16 +9980,16 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1311.458119432898</v>
+        <v>1382.215598825699</v>
       </c>
       <c r="F165" t="n">
-        <v>0.2622916238865795</v>
+        <v>0.2764431197651397</v>
       </c>
       <c r="G165" t="n">
-        <v>31.83591229064437</v>
+        <v>28.2979793567971</v>
       </c>
       <c r="H165" t="n">
-        <v>1.281085642037459e-14</v>
+        <v>1.340171589118595e-14</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>5000</v>
       </c>
       <c r="C166" t="n">
-        <v>5000.410375192505</v>
+        <v>5000.152346838676</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10038,16 +10038,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1490.547651373231</v>
+        <v>1460.333503344614</v>
       </c>
       <c r="F166" t="n">
-        <v>0.2981095302746462</v>
+        <v>0.2920667006689227</v>
       </c>
       <c r="G166" t="n">
-        <v>31.24909175998897</v>
+        <v>32.50848899219783</v>
       </c>
       <c r="H166" t="n">
-        <v>1.280070415534286e-14</v>
+        <v>1.263305234368961e-14</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>5000</v>
       </c>
       <c r="C167" t="n">
-        <v>5000.410375192505</v>
+        <v>5000.152346838676</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10096,16 +10096,16 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1345.142729462053</v>
+        <v>1328.985404533307</v>
       </c>
       <c r="F167" t="n">
-        <v>0.2690285458924107</v>
+        <v>0.2657970809066614</v>
       </c>
       <c r="G167" t="n">
-        <v>31.24909175998897</v>
+        <v>32.50848899219783</v>
       </c>
       <c r="H167" t="n">
-        <v>1.280070415534286e-14</v>
+        <v>1.263305234368961e-14</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>5000</v>
       </c>
       <c r="C168" t="n">
-        <v>5000.342052744649</v>
+        <v>5000.2006808067</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10154,16 +10154,16 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1464.580745368944</v>
+        <v>1517.374441867163</v>
       </c>
       <c r="F168" t="n">
-        <v>0.2929161490737889</v>
+        <v>0.3034748883734326</v>
       </c>
       <c r="G168" t="n">
-        <v>30.97429208975909</v>
+        <v>30.41911870881779</v>
       </c>
       <c r="H168" t="n">
-        <v>1.325244731928947e-14</v>
+        <v>1.324391125955494e-14</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>5000</v>
       </c>
       <c r="C169" t="n">
-        <v>5000.342052744649</v>
+        <v>5000.2006808067</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10212,16 +10212,16 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1329.983938076472</v>
+        <v>1389.9917488792</v>
       </c>
       <c r="F169" t="n">
-        <v>0.2659967876152945</v>
+        <v>0.27799834977584</v>
       </c>
       <c r="G169" t="n">
-        <v>30.97429208975909</v>
+        <v>30.41911870881779</v>
       </c>
       <c r="H169" t="n">
-        <v>1.325244731928947e-14</v>
+        <v>1.324391125955494e-14</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>5000</v>
       </c>
       <c r="C170" t="n">
-        <v>4999.557978764688</v>
+        <v>5000.353130063776</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10270,16 +10270,16 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1469.121731535334</v>
+        <v>1577.039787706684</v>
       </c>
       <c r="F170" t="n">
-        <v>0.2938243463070668</v>
+        <v>0.3154079575413367</v>
       </c>
       <c r="G170" t="n">
-        <v>32.9720062558518</v>
+        <v>29.53278143554217</v>
       </c>
       <c r="H170" t="n">
-        <v>1.249335782063962e-14</v>
+        <v>1.325718937780917e-14</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>5000</v>
       </c>
       <c r="C171" t="n">
-        <v>4999.557978764688</v>
+        <v>5000.353130063776</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10328,16 +10328,16 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1347.070589399171</v>
+        <v>1421.031241268099</v>
       </c>
       <c r="F171" t="n">
-        <v>0.2694141178798341</v>
+        <v>0.2842062482536198</v>
       </c>
       <c r="G171" t="n">
-        <v>32.9720062558518</v>
+        <v>29.53278143554217</v>
       </c>
       <c r="H171" t="n">
-        <v>1.249335782063962e-14</v>
+        <v>1.325718937780917e-14</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>5000</v>
       </c>
       <c r="C172" t="n">
-        <v>4999.500992119412</v>
+        <v>4999.470754511158</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10386,16 +10386,16 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1459.296384343973</v>
+        <v>1488.935024111792</v>
       </c>
       <c r="F172" t="n">
-        <v>0.2918592768687945</v>
+        <v>0.2977870048223584</v>
       </c>
       <c r="G172" t="n">
-        <v>31.83211851769653</v>
+        <v>30.41755518057504</v>
       </c>
       <c r="H172" t="n">
-        <v>1.2992837443153e-14</v>
+        <v>1.353989523157853e-14</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>5000</v>
       </c>
       <c r="C173" t="n">
-        <v>4999.500992119412</v>
+        <v>4999.470754511158</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10444,16 +10444,16 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1312.152465112096</v>
+        <v>1342.944313397693</v>
       </c>
       <c r="F173" t="n">
-        <v>0.2624304930224192</v>
+        <v>0.2685888626795386</v>
       </c>
       <c r="G173" t="n">
-        <v>31.83211851769653</v>
+        <v>30.41755518057504</v>
       </c>
       <c r="H173" t="n">
-        <v>1.2992837443153e-14</v>
+        <v>1.353989523157853e-14</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>5000</v>
       </c>
       <c r="C174" t="n">
-        <v>5000.23123012568</v>
+        <v>5000.496297943378</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10502,16 +10502,16 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1489.700132955325</v>
+        <v>1478.392587188017</v>
       </c>
       <c r="F174" t="n">
-        <v>0.2979400265910649</v>
+        <v>0.2956785174376034</v>
       </c>
       <c r="G174" t="n">
-        <v>31.81917473325312</v>
+        <v>30.92330351220811</v>
       </c>
       <c r="H174" t="n">
-        <v>1.29567360340236e-14</v>
+        <v>1.321890192660235e-14</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>5000</v>
       </c>
       <c r="C175" t="n">
-        <v>5000.23123012568</v>
+        <v>5000.496297943378</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10560,16 +10560,16 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1346.307415310383</v>
+        <v>1331.98262600816</v>
       </c>
       <c r="F175" t="n">
-        <v>0.2692614830620765</v>
+        <v>0.2663965252016319</v>
       </c>
       <c r="G175" t="n">
-        <v>31.81917473325312</v>
+        <v>30.92330351220811</v>
       </c>
       <c r="H175" t="n">
-        <v>1.29567360340236e-14</v>
+        <v>1.321890192660235e-14</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>5000</v>
       </c>
       <c r="C176" t="n">
-        <v>4999.944175275798</v>
+        <v>4999.294205018076</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10618,16 +10618,16 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1508.096818989403</v>
+        <v>1484.353367284962</v>
       </c>
       <c r="F176" t="n">
-        <v>0.3016193637978807</v>
+        <v>0.2968706734569924</v>
       </c>
       <c r="G176" t="n">
-        <v>30.77108847121994</v>
+        <v>30.69560104754948</v>
       </c>
       <c r="H176" t="n">
-        <v>1.327440787688589e-14</v>
+        <v>1.314722667881611e-14</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>5000</v>
       </c>
       <c r="C177" t="n">
-        <v>4999.944175275798</v>
+        <v>4999.294205018076</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10676,16 +10676,16 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1367.507198617951</v>
+        <v>1325.715175875171</v>
       </c>
       <c r="F177" t="n">
-        <v>0.2735014397235901</v>
+        <v>0.2651430351750341</v>
       </c>
       <c r="G177" t="n">
-        <v>30.77108847121994</v>
+        <v>30.69560104754948</v>
       </c>
       <c r="H177" t="n">
-        <v>1.327440787688589e-14</v>
+        <v>1.314722667881611e-14</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>5000</v>
       </c>
       <c r="C178" t="n">
-        <v>4999.074493350379</v>
+        <v>4999.616226624882</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -10734,16 +10734,16 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1462.791904414143</v>
+        <v>1502.047147056224</v>
       </c>
       <c r="F178" t="n">
-        <v>0.2925583808828285</v>
+        <v>0.3004094294112449</v>
       </c>
       <c r="G178" t="n">
-        <v>31.20634179437914</v>
+        <v>32.09398050567202</v>
       </c>
       <c r="H178" t="n">
-        <v>1.330682026913677e-14</v>
+        <v>1.293185185078731e-14</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>5000</v>
       </c>
       <c r="C179" t="n">
-        <v>4999.074493350379</v>
+        <v>4999.616226624882</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -10792,16 +10792,16 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1333.51590883121</v>
+        <v>1350.970918778451</v>
       </c>
       <c r="F179" t="n">
-        <v>0.2667031817662421</v>
+        <v>0.2701941837556903</v>
       </c>
       <c r="G179" t="n">
-        <v>31.20634179437914</v>
+        <v>32.09398050567202</v>
       </c>
       <c r="H179" t="n">
-        <v>1.330682026913677e-14</v>
+        <v>1.293185185078731e-14</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>5000</v>
       </c>
       <c r="C180" t="n">
-        <v>5000.018657670451</v>
+        <v>4999.17289346225</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -10850,16 +10850,16 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1435.284293378506</v>
+        <v>1494.60000958759</v>
       </c>
       <c r="F180" t="n">
-        <v>0.2870568586757011</v>
+        <v>0.2989200019175179</v>
       </c>
       <c r="G180" t="n">
-        <v>32.19596227156018</v>
+        <v>30.61186917812325</v>
       </c>
       <c r="H180" t="n">
-        <v>1.275353789380092e-14</v>
+        <v>1.328002404874235e-14</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>5000</v>
       </c>
       <c r="C181" t="n">
-        <v>5000.018657670451</v>
+        <v>4999.17289346225</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -10908,16 +10908,16 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1288.725750155102</v>
+        <v>1365.211823293425</v>
       </c>
       <c r="F181" t="n">
-        <v>0.2577451500310204</v>
+        <v>0.273042364658685</v>
       </c>
       <c r="G181" t="n">
-        <v>32.19596227156018</v>
+        <v>30.61186917812325</v>
       </c>
       <c r="H181" t="n">
-        <v>1.275353789380092e-14</v>
+        <v>1.328002404874235e-14</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>5000</v>
       </c>
       <c r="C182" t="n">
-        <v>5000.223363635127</v>
+        <v>4998.961780529766</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -10966,16 +10966,16 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1665.603488689934</v>
+        <v>1724.201762185028</v>
       </c>
       <c r="F182" t="n">
-        <v>0.3331206977379867</v>
+        <v>0.3448403524370055</v>
       </c>
       <c r="G182" t="n">
-        <v>24.76162218910468</v>
+        <v>24.6198125271147</v>
       </c>
       <c r="H182" t="n">
-        <v>2.078419620416466e-14</v>
+        <v>2.057397172500127e-14</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>5000</v>
       </c>
       <c r="C183" t="n">
-        <v>5000.223363635127</v>
+        <v>4998.961780529766</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11024,16 +11024,16 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1526.817526338664</v>
+        <v>1545.17326174739</v>
       </c>
       <c r="F183" t="n">
-        <v>0.3053635052677328</v>
+        <v>0.309034652349478</v>
       </c>
       <c r="G183" t="n">
-        <v>24.76162218910468</v>
+        <v>24.6198125271147</v>
       </c>
       <c r="H183" t="n">
-        <v>2.078419620416466e-14</v>
+        <v>2.057397172500127e-14</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>5000</v>
       </c>
       <c r="C184" t="n">
-        <v>4999.96066740576</v>
+        <v>4999.91317396603</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11082,16 +11082,16 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1686.669562486033</v>
+        <v>1675.015705475811</v>
       </c>
       <c r="F184" t="n">
-        <v>0.3373339124972066</v>
+        <v>0.3350031410951622</v>
       </c>
       <c r="G184" t="n">
-        <v>25.06994342009447</v>
+        <v>23.36846381218427</v>
       </c>
       <c r="H184" t="n">
-        <v>2.032930923345556e-14</v>
+        <v>2.07535479474599e-14</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>5000</v>
       </c>
       <c r="C185" t="n">
-        <v>4999.96066740576</v>
+        <v>4999.91317396603</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11140,16 +11140,16 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1509.941687988695</v>
+        <v>1508.465132334266</v>
       </c>
       <c r="F185" t="n">
-        <v>0.301988337597739</v>
+        <v>0.3016930264668532</v>
       </c>
       <c r="G185" t="n">
-        <v>25.06994342009447</v>
+        <v>23.36846381218427</v>
       </c>
       <c r="H185" t="n">
-        <v>2.032930923345556e-14</v>
+        <v>2.07535479474599e-14</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>5000</v>
       </c>
       <c r="C186" t="n">
-        <v>4999.367799682511</v>
+        <v>5000.091580715882</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11198,16 +11198,16 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1782.462954179232</v>
+        <v>1639.150941648515</v>
       </c>
       <c r="F186" t="n">
-        <v>0.3564925908358464</v>
+        <v>0.327830188329703</v>
       </c>
       <c r="G186" t="n">
-        <v>23.56431892718903</v>
+        <v>25.63470379428088</v>
       </c>
       <c r="H186" t="n">
-        <v>2.117326683483654e-14</v>
+        <v>1.989814581967696e-14</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>5000</v>
       </c>
       <c r="C187" t="n">
-        <v>4999.367799682511</v>
+        <v>5000.091580715882</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11256,16 +11256,16 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1563.994194034329</v>
+        <v>1480.474205541181</v>
       </c>
       <c r="F187" t="n">
-        <v>0.3127988388068658</v>
+        <v>0.2960948411082362</v>
       </c>
       <c r="G187" t="n">
-        <v>23.56431892718903</v>
+        <v>25.63470379428088</v>
       </c>
       <c r="H187" t="n">
-        <v>2.117326683483654e-14</v>
+        <v>1.989814581967696e-14</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>5000</v>
       </c>
       <c r="C188" t="n">
-        <v>5000.032986364216</v>
+        <v>5000.406143422696</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11314,16 +11314,16 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1656.670984752355</v>
+        <v>1657.791862044384</v>
       </c>
       <c r="F188" t="n">
-        <v>0.331334196950471</v>
+        <v>0.3315583724088768</v>
       </c>
       <c r="G188" t="n">
-        <v>25.40338343736325</v>
+        <v>23.87472908731909</v>
       </c>
       <c r="H188" t="n">
-        <v>2.026143506356974e-14</v>
+        <v>2.010896451616328e-14</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>5000</v>
       </c>
       <c r="C189" t="n">
-        <v>5000.032986364216</v>
+        <v>5000.406143422696</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11372,16 +11372,16 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1484.802753883299</v>
+        <v>1482.129471436236</v>
       </c>
       <c r="F189" t="n">
-        <v>0.2969605507766597</v>
+        <v>0.2964258942872472</v>
       </c>
       <c r="G189" t="n">
-        <v>25.40338343736325</v>
+        <v>23.87472908731909</v>
       </c>
       <c r="H189" t="n">
-        <v>2.026143506356974e-14</v>
+        <v>2.010896451616328e-14</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>5000</v>
       </c>
       <c r="C190" t="n">
-        <v>4999.944165518049</v>
+        <v>4999.810148415683</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11430,16 +11430,16 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1607.515687549828</v>
+        <v>1696.399376120845</v>
       </c>
       <c r="F190" t="n">
-        <v>0.3215031375099656</v>
+        <v>0.3392798752241691</v>
       </c>
       <c r="G190" t="n">
-        <v>25.69304677073833</v>
+        <v>25.105578360575</v>
       </c>
       <c r="H190" t="n">
-        <v>1.999226863764232e-14</v>
+        <v>2.064412010363113e-14</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>5000</v>
       </c>
       <c r="C191" t="n">
-        <v>4999.944165518049</v>
+        <v>4999.810148415683</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11488,16 +11488,16 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1476.050196031504</v>
+        <v>1513.221437887831</v>
       </c>
       <c r="F191" t="n">
-        <v>0.2952100392063008</v>
+        <v>0.3026442875775661</v>
       </c>
       <c r="G191" t="n">
-        <v>25.69304677073833</v>
+        <v>25.105578360575</v>
       </c>
       <c r="H191" t="n">
-        <v>1.999226863764232e-14</v>
+        <v>2.064412010363113e-14</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>5000</v>
       </c>
       <c r="C192" t="n">
-        <v>5000.434299278622</v>
+        <v>4999.650714972392</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11546,16 +11546,16 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1669.110277626673</v>
+        <v>1675.70610068368</v>
       </c>
       <c r="F192" t="n">
-        <v>0.3338220555253345</v>
+        <v>0.3351412201367361</v>
       </c>
       <c r="G192" t="n">
-        <v>24.71204832068381</v>
+        <v>25.39931513514036</v>
       </c>
       <c r="H192" t="n">
-        <v>2.120312099984612e-14</v>
+        <v>1.997316815105327e-14</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>5000</v>
       </c>
       <c r="C193" t="n">
-        <v>5000.434299278622</v>
+        <v>4999.650714972392</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11604,16 +11604,16 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1534.028820154244</v>
+        <v>1521.40332561686</v>
       </c>
       <c r="F193" t="n">
-        <v>0.3068057640308487</v>
+        <v>0.304280665123372</v>
       </c>
       <c r="G193" t="n">
-        <v>24.71204832068381</v>
+        <v>25.39931513514036</v>
       </c>
       <c r="H193" t="n">
-        <v>2.120312099984612e-14</v>
+        <v>1.997316815105327e-14</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>5000</v>
       </c>
       <c r="C194" t="n">
-        <v>4999.685575409319</v>
+        <v>5000.394696650464</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11662,16 +11662,16 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1678.263045277828</v>
+        <v>1664.152469309065</v>
       </c>
       <c r="F194" t="n">
-        <v>0.3356526090555656</v>
+        <v>0.3328304938618131</v>
       </c>
       <c r="G194" t="n">
-        <v>26.17546588278525</v>
+        <v>25.94562649888062</v>
       </c>
       <c r="H194" t="n">
-        <v>1.942669190130084e-14</v>
+        <v>1.987618651803086e-14</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>5000</v>
       </c>
       <c r="C195" t="n">
-        <v>4999.685575409319</v>
+        <v>5000.394696650464</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -11720,16 +11720,16 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1531.266270989494</v>
+        <v>1497.821468349517</v>
       </c>
       <c r="F195" t="n">
-        <v>0.3062532541978989</v>
+        <v>0.2995642936699033</v>
       </c>
       <c r="G195" t="n">
-        <v>26.17546588278525</v>
+        <v>25.94562649888062</v>
       </c>
       <c r="H195" t="n">
-        <v>1.942669190130084e-14</v>
+        <v>1.987618651803086e-14</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>5000</v>
       </c>
       <c r="C196" t="n">
-        <v>4999.433396472633</v>
+        <v>4998.727604937744</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -11778,16 +11778,16 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1730.865431302108</v>
+        <v>1683.018593303208</v>
       </c>
       <c r="F196" t="n">
-        <v>0.3461730862604216</v>
+        <v>0.3366037186606417</v>
       </c>
       <c r="G196" t="n">
-        <v>23.39105529953307</v>
+        <v>25.15293019184302</v>
       </c>
       <c r="H196" t="n">
-        <v>2.088494860638346e-14</v>
+        <v>2.075539461939657e-14</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>5000</v>
       </c>
       <c r="C197" t="n">
-        <v>4999.433396472633</v>
+        <v>4998.727604937744</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -11836,16 +11836,16 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1519.006486054987</v>
+        <v>1509.963358842185</v>
       </c>
       <c r="F197" t="n">
-        <v>0.3038012972109975</v>
+        <v>0.301992671768437</v>
       </c>
       <c r="G197" t="n">
-        <v>23.39105529953307</v>
+        <v>25.15293019184302</v>
       </c>
       <c r="H197" t="n">
-        <v>2.088494860638346e-14</v>
+        <v>2.075539461939657e-14</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>5000</v>
       </c>
       <c r="C198" t="n">
-        <v>4999.922170306473</v>
+        <v>5000.256012261762</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -11894,16 +11894,16 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1695.206487844117</v>
+        <v>1710.867783415274</v>
       </c>
       <c r="F198" t="n">
-        <v>0.3390412975688234</v>
+        <v>0.3421735566830548</v>
       </c>
       <c r="G198" t="n">
-        <v>23.96511578408137</v>
+        <v>24.16011892691082</v>
       </c>
       <c r="H198" t="n">
-        <v>2.139004394003518e-14</v>
+        <v>2.062634246847841e-14</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>5000</v>
       </c>
       <c r="C199" t="n">
-        <v>4999.922170306473</v>
+        <v>5000.256012261762</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -11952,16 +11952,16 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1542.382627996562</v>
+        <v>1537.678569807046</v>
       </c>
       <c r="F199" t="n">
-        <v>0.3084765255993125</v>
+        <v>0.3075357139614092</v>
       </c>
       <c r="G199" t="n">
-        <v>23.96511578408137</v>
+        <v>24.16011892691082</v>
       </c>
       <c r="H199" t="n">
-        <v>2.139004394003518e-14</v>
+        <v>2.062634246847841e-14</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>5000</v>
       </c>
       <c r="C200" t="n">
-        <v>4999.464373213726</v>
+        <v>4999.751079384153</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12010,16 +12010,16 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1734.567390411057</v>
+        <v>1653.646123543074</v>
       </c>
       <c r="F200" t="n">
-        <v>0.3469134780822115</v>
+        <v>0.3307292247086148</v>
       </c>
       <c r="G200" t="n">
-        <v>24.9484848212647</v>
+        <v>23.89342092296229</v>
       </c>
       <c r="H200" t="n">
-        <v>2.033479857104911e-14</v>
+        <v>2.084268910247762e-14</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>5000</v>
       </c>
       <c r="C201" t="n">
-        <v>4999.464373213726</v>
+        <v>4999.751079384153</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12068,16 +12068,16 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1594.59427572966</v>
+        <v>1499.701479803861</v>
       </c>
       <c r="F201" t="n">
-        <v>0.3189188551459321</v>
+        <v>0.2999402959607722</v>
       </c>
       <c r="G201" t="n">
-        <v>24.9484848212647</v>
+        <v>23.89342092296229</v>
       </c>
       <c r="H201" t="n">
-        <v>2.033479857104911e-14</v>
+        <v>2.084268910247762e-14</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>10000</v>
       </c>
       <c r="C202" t="n">
-        <v>9997.070323986216</v>
+        <v>10005.48674774612</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12126,16 +12126,16 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1168.141631988114</v>
+        <v>1079.518636147865</v>
       </c>
       <c r="F202" t="n">
-        <v>0.1168141631988114</v>
+        <v>0.1079518636147866</v>
       </c>
       <c r="G202" t="n">
-        <v>159.5682161713257</v>
+        <v>202</v>
       </c>
       <c r="H202" t="n">
-        <v>2.920309629728179e-17</v>
+        <v>4.355306237713761e-17</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>10000</v>
       </c>
       <c r="C203" t="n">
-        <v>9997.070323986216</v>
+        <v>10005.48674774612</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12184,16 +12184,16 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1060.510784532644</v>
+        <v>984.2902063161326</v>
       </c>
       <c r="F203" t="n">
-        <v>0.1060510784532644</v>
+        <v>0.09842902063161327</v>
       </c>
       <c r="G203" t="n">
-        <v>159.5682161713257</v>
+        <v>202</v>
       </c>
       <c r="H203" t="n">
-        <v>2.920309629728179e-17</v>
+        <v>4.355306237713761e-17</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>10000</v>
       </c>
       <c r="C204" t="n">
-        <v>9998.872787685837</v>
+        <v>9985.702560845164</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12242,16 +12242,16 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1149.362613405453</v>
+        <v>1083.947399633258</v>
       </c>
       <c r="F204" t="n">
-        <v>0.1149362613405452</v>
+        <v>0.1083947399633258</v>
       </c>
       <c r="G204" t="n">
-        <v>169.7174758510679</v>
+        <v>202</v>
       </c>
       <c r="H204" t="n">
-        <v>2.991358780111658e-17</v>
+        <v>2.865319335966263e-17</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>10000</v>
       </c>
       <c r="C205" t="n">
-        <v>9998.872787685837</v>
+        <v>9985.702560845164</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12300,16 +12300,16 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1039.273292415795</v>
+        <v>979.2770123819885</v>
       </c>
       <c r="F205" t="n">
-        <v>0.1039273292415795</v>
+        <v>0.09792770123819884</v>
       </c>
       <c r="G205" t="n">
-        <v>169.7174758510679</v>
+        <v>202</v>
       </c>
       <c r="H205" t="n">
-        <v>2.991358780111658e-17</v>
+        <v>2.865319335966263e-17</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>10000</v>
       </c>
       <c r="C206" t="n">
-        <v>9993.45613242979</v>
+        <v>10017.48578419875</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12358,16 +12358,16 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1083.915215563048</v>
+        <v>1078.645301661807</v>
       </c>
       <c r="F206" t="n">
-        <v>0.1083915215563048</v>
+        <v>0.1078645301661807</v>
       </c>
       <c r="G206" t="n">
-        <v>202</v>
+        <v>201.9999999999964</v>
       </c>
       <c r="H206" t="n">
-        <v>3.460174859503021e-17</v>
+        <v>2.846490122499489e-17</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>10000</v>
       </c>
       <c r="C207" t="n">
-        <v>9993.45613242979</v>
+        <v>10017.48578419875</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12416,16 +12416,16 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>980.7453180210264</v>
+        <v>979.8060094396312</v>
       </c>
       <c r="F207" t="n">
-        <v>0.09807453180210264</v>
+        <v>0.09798060094396312</v>
       </c>
       <c r="G207" t="n">
-        <v>202</v>
+        <v>201.9999999999964</v>
       </c>
       <c r="H207" t="n">
-        <v>3.460174859503021e-17</v>
+        <v>2.846490122499489e-17</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>10000</v>
       </c>
       <c r="C208" t="n">
-        <v>9996.361685822038</v>
+        <v>10002.81298891064</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12474,16 +12474,16 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1165.290779904996</v>
+        <v>1188.309956159358</v>
       </c>
       <c r="F208" t="n">
-        <v>0.1165290779904996</v>
+        <v>0.1188309956159358</v>
       </c>
       <c r="G208" t="n">
-        <v>158.4513282202</v>
+        <v>152.0338969036164</v>
       </c>
       <c r="H208" t="n">
-        <v>3.150204614009119e-17</v>
+        <v>3.033599689971462e-17</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>10000</v>
       </c>
       <c r="C209" t="n">
-        <v>9996.361685822038</v>
+        <v>10002.81298891064</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12532,16 +12532,16 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1055.574206188015</v>
+        <v>1070.605633537406</v>
       </c>
       <c r="F209" t="n">
-        <v>0.1055574206188015</v>
+        <v>0.1070605633537405</v>
       </c>
       <c r="G209" t="n">
-        <v>158.4513282202</v>
+        <v>152.0338969036164</v>
       </c>
       <c r="H209" t="n">
-        <v>3.150204614009119e-17</v>
+        <v>3.033599689971462e-17</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>10000</v>
       </c>
       <c r="C210" t="n">
-        <v>9998.096081595837</v>
+        <v>9990.135473638502</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12590,16 +12590,16 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1084.651122577094</v>
+        <v>1154.308277154985</v>
       </c>
       <c r="F210" t="n">
-        <v>0.1084651122577094</v>
+        <v>0.1154308277154985</v>
       </c>
       <c r="G210" t="n">
-        <v>202</v>
+        <v>157.8384665824855</v>
       </c>
       <c r="H210" t="n">
-        <v>5.265316611409572e-17</v>
+        <v>2.903985548369792e-17</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>10000</v>
       </c>
       <c r="C211" t="n">
-        <v>9998.096081595837</v>
+        <v>9990.135473638502</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12648,16 +12648,16 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>985.6747516564423</v>
+        <v>1053.913597905276</v>
       </c>
       <c r="F211" t="n">
-        <v>0.09856747516564422</v>
+        <v>0.1053913597905276</v>
       </c>
       <c r="G211" t="n">
-        <v>202</v>
+        <v>157.8384665824855</v>
       </c>
       <c r="H211" t="n">
-        <v>5.265316611409572e-17</v>
+        <v>2.903985548369792e-17</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>10000</v>
       </c>
       <c r="C212" t="n">
-        <v>9993.980321592675</v>
+        <v>9989.570711112354</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -12706,16 +12706,16 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1080.202113024992</v>
+        <v>1089.314202929571</v>
       </c>
       <c r="F212" t="n">
-        <v>0.1080202113024992</v>
+        <v>0.1089314202929571</v>
       </c>
       <c r="G212" t="n">
-        <v>202</v>
+        <v>201.9999999999999</v>
       </c>
       <c r="H212" t="n">
-        <v>4.399364459011177e-17</v>
+        <v>3.724351690005167e-17</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>10000</v>
       </c>
       <c r="C213" t="n">
-        <v>9993.980321592675</v>
+        <v>9989.570711112354</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -12764,16 +12764,16 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>978.8407318361649</v>
+        <v>985.7611993463751</v>
       </c>
       <c r="F213" t="n">
-        <v>0.09788407318361649</v>
+        <v>0.09857611993463751</v>
       </c>
       <c r="G213" t="n">
-        <v>202</v>
+        <v>201.9999999999999</v>
       </c>
       <c r="H213" t="n">
-        <v>4.399364459011177e-17</v>
+        <v>3.724351690005167e-17</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>10000</v>
       </c>
       <c r="C214" t="n">
-        <v>9992.945707044766</v>
+        <v>9994.665969689491</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -12822,16 +12822,16 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1089.173537812749</v>
+        <v>1092.423447585058</v>
       </c>
       <c r="F214" t="n">
-        <v>0.1089173537812749</v>
+        <v>0.1092423447585057</v>
       </c>
       <c r="G214" t="n">
-        <v>201.9999999999748</v>
+        <v>202</v>
       </c>
       <c r="H214" t="n">
-        <v>2.848798036254785e-17</v>
+        <v>3.221915863501811e-17</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>10000</v>
       </c>
       <c r="C215" t="n">
-        <v>9992.945707044766</v>
+        <v>9994.665969689491</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -12880,16 +12880,16 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>982.2102253521823</v>
+        <v>984.99371710757</v>
       </c>
       <c r="F215" t="n">
-        <v>0.09822102253521824</v>
+        <v>0.098499371710757</v>
       </c>
       <c r="G215" t="n">
-        <v>201.9999999999748</v>
+        <v>202</v>
       </c>
       <c r="H215" t="n">
-        <v>2.848798036254785e-17</v>
+        <v>3.221915863501811e-17</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>10000</v>
       </c>
       <c r="C216" t="n">
-        <v>9991.099606961776</v>
+        <v>10000.42371606933</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -12938,16 +12938,16 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1088.39434725945</v>
+        <v>1089.385635898181</v>
       </c>
       <c r="F216" t="n">
-        <v>0.108839434725945</v>
+        <v>0.1089385635898181</v>
       </c>
       <c r="G216" t="n">
-        <v>201.9999999999997</v>
+        <v>201.8622983419861</v>
       </c>
       <c r="H216" t="n">
-        <v>2.942018387437118e-17</v>
+        <v>5.348195475051897e-17</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>10000</v>
       </c>
       <c r="C217" t="n">
-        <v>9991.099606961776</v>
+        <v>10000.42371606933</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -12996,16 +12996,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>985.2092161212033</v>
+        <v>984.5547415443697</v>
       </c>
       <c r="F217" t="n">
-        <v>0.09852092161212034</v>
+        <v>0.09845547415443696</v>
       </c>
       <c r="G217" t="n">
-        <v>201.9999999999997</v>
+        <v>201.8622983419861</v>
       </c>
       <c r="H217" t="n">
-        <v>2.942018387437118e-17</v>
+        <v>5.348195475051897e-17</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>10000</v>
       </c>
       <c r="C218" t="n">
-        <v>9997.660561299435</v>
+        <v>10010.50548234635</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13054,16 +13054,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1079.567149572753</v>
+        <v>1094.466640502781</v>
       </c>
       <c r="F218" t="n">
-        <v>0.1079567149572753</v>
+        <v>0.1094466640502781</v>
       </c>
       <c r="G218" t="n">
         <v>202</v>
       </c>
       <c r="H218" t="n">
-        <v>4.499524644746585e-17</v>
+        <v>3.848828690912578e-17</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>10000</v>
       </c>
       <c r="C219" t="n">
-        <v>9997.660561299435</v>
+        <v>10010.50548234635</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13112,16 +13112,16 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>981.2509947791738</v>
+        <v>989.4318270670743</v>
       </c>
       <c r="F219" t="n">
-        <v>0.09812509947791738</v>
+        <v>0.09894318270670743</v>
       </c>
       <c r="G219" t="n">
         <v>202</v>
       </c>
       <c r="H219" t="n">
-        <v>4.499524644746585e-17</v>
+        <v>3.848828690912578e-17</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>10000</v>
       </c>
       <c r="C220" t="n">
-        <v>10008.7736765489</v>
+        <v>9998.017308291308</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13170,16 +13170,16 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1165.20469696797</v>
+        <v>1173.141671351533</v>
       </c>
       <c r="F220" t="n">
-        <v>0.116520469696797</v>
+        <v>0.1173141671351533</v>
       </c>
       <c r="G220" t="n">
-        <v>158.1734174121731</v>
+        <v>157.868588588377</v>
       </c>
       <c r="H220" t="n">
-        <v>2.824158684269344e-17</v>
+        <v>3.001245215586101e-17</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>10000</v>
       </c>
       <c r="C221" t="n">
-        <v>10008.7736765489</v>
+        <v>9998.017308291308</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13228,16 +13228,16 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1057.138488683014</v>
+        <v>1065.749734202043</v>
       </c>
       <c r="F221" t="n">
-        <v>0.1057138488683014</v>
+        <v>0.1065749734202043</v>
       </c>
       <c r="G221" t="n">
-        <v>158.1734174121731</v>
+        <v>157.868588588377</v>
       </c>
       <c r="H221" t="n">
-        <v>2.824158684269344e-17</v>
+        <v>3.001245215586101e-17</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>10000</v>
       </c>
       <c r="C222" t="n">
-        <v>10002.0905868605</v>
+        <v>10000.55037359481</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13286,16 +13286,16 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1510.590681796919</v>
+        <v>1493.48613160759</v>
       </c>
       <c r="F222" t="n">
-        <v>0.1510590681796919</v>
+        <v>0.149348613160759</v>
       </c>
       <c r="G222" t="n">
-        <v>103.1112795713527</v>
+        <v>117.4280855075184</v>
       </c>
       <c r="H222" t="n">
-        <v>1.553055153389633e-16</v>
+        <v>2.035978215200465e-16</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>10000</v>
       </c>
       <c r="C223" t="n">
-        <v>10002.0905868605</v>
+        <v>10000.55037359481</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13344,16 +13344,16 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1369.053519069073</v>
+        <v>1348.313701974662</v>
       </c>
       <c r="F223" t="n">
-        <v>0.1369053519069073</v>
+        <v>0.1348313701974662</v>
       </c>
       <c r="G223" t="n">
-        <v>103.1112795713527</v>
+        <v>117.4280855075184</v>
       </c>
       <c r="H223" t="n">
-        <v>1.553055153389633e-16</v>
+        <v>2.035978215200465e-16</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>10000</v>
       </c>
       <c r="C224" t="n">
-        <v>10000.73556437116</v>
+        <v>10000.79619243324</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13402,16 +13402,16 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1478.101698317466</v>
+        <v>1618.376953467037</v>
       </c>
       <c r="F224" t="n">
-        <v>0.1478101698317466</v>
+        <v>0.1618376953467037</v>
       </c>
       <c r="G224" t="n">
-        <v>127.954080878891</v>
+        <v>91.1229509641918</v>
       </c>
       <c r="H224" t="n">
-        <v>2.062549618651202e-16</v>
+        <v>1.609495319083133e-16</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>10000</v>
       </c>
       <c r="C225" t="n">
-        <v>10000.73556437116</v>
+        <v>10000.79619243324</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13460,16 +13460,16 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>1320.119191299261</v>
+        <v>1457.442849528242</v>
       </c>
       <c r="F225" t="n">
-        <v>0.1320119191299261</v>
+        <v>0.1457442849528242</v>
       </c>
       <c r="G225" t="n">
-        <v>127.954080878891</v>
+        <v>91.1229509641918</v>
       </c>
       <c r="H225" t="n">
-        <v>2.062549618651202e-16</v>
+        <v>1.609495319083133e-16</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>10000</v>
       </c>
       <c r="C226" t="n">
-        <v>9999.272975750389</v>
+        <v>9997.665095003831</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13518,16 +13518,16 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1480.066415637155</v>
+        <v>1480.858626931643</v>
       </c>
       <c r="F226" t="n">
-        <v>0.1480066415637155</v>
+        <v>0.1480858626931643</v>
       </c>
       <c r="G226" t="n">
-        <v>122.3611228557728</v>
+        <v>124.4450456792906</v>
       </c>
       <c r="H226" t="n">
-        <v>2.058274203182116e-16</v>
+        <v>2.078458176315172e-16</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>10000</v>
       </c>
       <c r="C227" t="n">
-        <v>9999.272975750389</v>
+        <v>9997.665095003831</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13576,16 +13576,16 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1331.037810524629</v>
+        <v>1341.388183619845</v>
       </c>
       <c r="F227" t="n">
-        <v>0.1331037810524629</v>
+        <v>0.1341388183619845</v>
       </c>
       <c r="G227" t="n">
-        <v>122.3611228557728</v>
+        <v>124.4450456792906</v>
       </c>
       <c r="H227" t="n">
-        <v>2.058274203182116e-16</v>
+        <v>2.078458176315172e-16</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>10000</v>
       </c>
       <c r="C228" t="n">
-        <v>9999.755287568092</v>
+        <v>9999.456808006407</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13634,16 +13634,16 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1482.016266387337</v>
+        <v>1760.678138779244</v>
       </c>
       <c r="F228" t="n">
-        <v>0.1482016266387337</v>
+        <v>0.1760678138779244</v>
       </c>
       <c r="G228" t="n">
-        <v>118.7476876395889</v>
+        <v>67.72093636823908</v>
       </c>
       <c r="H228" t="n">
-        <v>1.896829065010443e-16</v>
+        <v>1.317648848368023e-16</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>10000</v>
       </c>
       <c r="C229" t="n">
-        <v>9999.755287568092</v>
+        <v>9999.456808006407</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13692,16 +13692,16 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1336.343317768937</v>
+        <v>1608.374732431508</v>
       </c>
       <c r="F229" t="n">
-        <v>0.1336343317768937</v>
+        <v>0.1608374732431508</v>
       </c>
       <c r="G229" t="n">
-        <v>118.7476876395889</v>
+        <v>67.72093636823908</v>
       </c>
       <c r="H229" t="n">
-        <v>1.896829065010443e-16</v>
+        <v>1.317648848368023e-16</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>10000</v>
       </c>
       <c r="C230" t="n">
-        <v>9994.279764497251</v>
+        <v>9998.054506740571</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -13750,16 +13750,16 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>1514.070800856447</v>
+        <v>1468.173741425743</v>
       </c>
       <c r="F230" t="n">
-        <v>0.1514070800856447</v>
+        <v>0.1468173741425743</v>
       </c>
       <c r="G230" t="n">
-        <v>105.2968703775995</v>
+        <v>125.9842674152687</v>
       </c>
       <c r="H230" t="n">
-        <v>1.805407347122376e-16</v>
+        <v>2.073878344481893e-16</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>10000</v>
       </c>
       <c r="C231" t="n">
-        <v>9994.279764497251</v>
+        <v>9998.054506740571</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -13808,16 +13808,16 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>1367.453943000038</v>
+        <v>1328.351188471175</v>
       </c>
       <c r="F231" t="n">
-        <v>0.1367453943000038</v>
+        <v>0.1328351188471175</v>
       </c>
       <c r="G231" t="n">
-        <v>105.2968703775995</v>
+        <v>125.9842674152687</v>
       </c>
       <c r="H231" t="n">
-        <v>1.805407347122376e-16</v>
+        <v>2.073878344481893e-16</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>10000</v>
       </c>
       <c r="C232" t="n">
-        <v>10000.41295984779</v>
+        <v>10002.13047289982</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -13866,16 +13866,16 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1514.192164284676</v>
+        <v>1560.174140735952</v>
       </c>
       <c r="F232" t="n">
-        <v>0.1514192164284676</v>
+        <v>0.1560174140735952</v>
       </c>
       <c r="G232" t="n">
-        <v>107.4583529273</v>
+        <v>99.69755465124638</v>
       </c>
       <c r="H232" t="n">
-        <v>1.773409172076753e-16</v>
+        <v>1.548793364243474e-16</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>10000</v>
       </c>
       <c r="C233" t="n">
-        <v>10000.41295984779</v>
+        <v>10002.13047289982</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -13924,16 +13924,16 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1371.382597267616</v>
+        <v>1413.291592317835</v>
       </c>
       <c r="F233" t="n">
-        <v>0.1371382597267616</v>
+        <v>0.1413291592317835</v>
       </c>
       <c r="G233" t="n">
-        <v>107.4583529273</v>
+        <v>99.69755465124638</v>
       </c>
       <c r="H233" t="n">
-        <v>1.773409172076753e-16</v>
+        <v>1.548793364243474e-16</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>10000</v>
       </c>
       <c r="C234" t="n">
-        <v>10000.69935016598</v>
+        <v>9997.491501817152</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -13982,16 +13982,16 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1472.445347748329</v>
+        <v>1471.905702246669</v>
       </c>
       <c r="F234" t="n">
-        <v>0.1472445347748329</v>
+        <v>0.1471905702246669</v>
       </c>
       <c r="G234" t="n">
-        <v>126.0140075927844</v>
+        <v>120.4964529969158</v>
       </c>
       <c r="H234" t="n">
-        <v>2.030517155004452e-16</v>
+        <v>2.090988999714635e-16</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>10000</v>
       </c>
       <c r="C235" t="n">
-        <v>10000.69935016598</v>
+        <v>9997.491501817152</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14040,16 +14040,16 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>1324.792332146561</v>
+        <v>1326.761427267262</v>
       </c>
       <c r="F235" t="n">
-        <v>0.132479233214656</v>
+        <v>0.1326761427267261</v>
       </c>
       <c r="G235" t="n">
-        <v>126.0140075927844</v>
+        <v>120.4964529969158</v>
       </c>
       <c r="H235" t="n">
-        <v>2.030517155004452e-16</v>
+        <v>2.090988999714635e-16</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>10000</v>
       </c>
       <c r="C236" t="n">
-        <v>9999.100797878898</v>
+        <v>9999.735759082652</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14098,16 +14098,16 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>1490.070738384722</v>
+        <v>1456.095248402784</v>
       </c>
       <c r="F236" t="n">
-        <v>0.1490070738384722</v>
+        <v>0.1456095248402784</v>
       </c>
       <c r="G236" t="n">
-        <v>119.8600364674764</v>
+        <v>128.0932252832203</v>
       </c>
       <c r="H236" t="n">
-        <v>2.102109295250549e-16</v>
+        <v>2.036443908130363e-16</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>10000</v>
       </c>
       <c r="C237" t="n">
-        <v>9999.100797878898</v>
+        <v>9999.735759082652</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14156,16 +14156,16 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>1341.013317002391</v>
+        <v>1318.184732240282</v>
       </c>
       <c r="F237" t="n">
-        <v>0.1341013317002391</v>
+        <v>0.1318184732240282</v>
       </c>
       <c r="G237" t="n">
-        <v>119.8600364674764</v>
+        <v>128.0932252832203</v>
       </c>
       <c r="H237" t="n">
-        <v>2.102109295250549e-16</v>
+        <v>2.036443908130363e-16</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>10000</v>
       </c>
       <c r="C238" t="n">
-        <v>10000.42436046504</v>
+        <v>9998.639992795397</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14214,16 +14214,16 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>1467.941424565156</v>
+        <v>1540.403165901034</v>
       </c>
       <c r="F238" t="n">
-        <v>0.1467941424565156</v>
+        <v>0.1540403165901034</v>
       </c>
       <c r="G238" t="n">
-        <v>120.3205977597249</v>
+        <v>102.1453158768793</v>
       </c>
       <c r="H238" t="n">
-        <v>2.068910957321835e-16</v>
+        <v>1.619638865352428e-16</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>10000</v>
       </c>
       <c r="C239" t="n">
-        <v>10000.42436046504</v>
+        <v>9998.639992795397</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14272,16 +14272,16 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1331.221638450571</v>
+        <v>1403.108493263034</v>
       </c>
       <c r="F239" t="n">
-        <v>0.1331221638450571</v>
+        <v>0.1403108493263034</v>
       </c>
       <c r="G239" t="n">
-        <v>120.3205977597249</v>
+        <v>102.1453158768793</v>
       </c>
       <c r="H239" t="n">
-        <v>2.068910957321835e-16</v>
+        <v>1.619638865352428e-16</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>10000</v>
       </c>
       <c r="C240" t="n">
-        <v>10001.08387629157</v>
+        <v>9996.567718195873</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14330,16 +14330,16 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1549.106326410905</v>
+        <v>1470.910225966029</v>
       </c>
       <c r="F240" t="n">
-        <v>0.1549106326410905</v>
+        <v>0.1470910225966029</v>
       </c>
       <c r="G240" t="n">
-        <v>98.17522748557907</v>
+        <v>125.0402964868399</v>
       </c>
       <c r="H240" t="n">
-        <v>1.517344036628799e-16</v>
+        <v>2.056430390481904e-16</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>10000</v>
       </c>
       <c r="C241" t="n">
-        <v>10001.08387629157</v>
+        <v>9996.567718195873</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14388,16 +14388,16 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1396.626567391716</v>
+        <v>1335.113772409582</v>
       </c>
       <c r="F241" t="n">
-        <v>0.1396626567391716</v>
+        <v>0.1335113772409582</v>
       </c>
       <c r="G241" t="n">
-        <v>98.17522748557907</v>
+        <v>125.0402964868399</v>
       </c>
       <c r="H241" t="n">
-        <v>1.517344036628799e-16</v>
+        <v>2.056430390481904e-16</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>10000</v>
       </c>
       <c r="C242" t="n">
-        <v>9999.033625693979</v>
+        <v>9998.960145948477</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14446,16 +14446,16 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1833.326818678721</v>
+        <v>1835.167662739624</v>
       </c>
       <c r="F242" t="n">
-        <v>0.1833326818678721</v>
+        <v>0.1835167662739624</v>
       </c>
       <c r="G242" t="n">
-        <v>82.44901614226491</v>
+        <v>78.18188797937262</v>
       </c>
       <c r="H242" t="n">
-        <v>4.657913275941738e-16</v>
+        <v>4.43329544266233e-16</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>10000</v>
       </c>
       <c r="C243" t="n">
-        <v>9999.033625693979</v>
+        <v>9998.960145948477</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14504,16 +14504,16 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1660.338974209703</v>
+        <v>1642.115999849685</v>
       </c>
       <c r="F243" t="n">
-        <v>0.1660338974209703</v>
+        <v>0.1642115999849685</v>
       </c>
       <c r="G243" t="n">
-        <v>82.44901614226491</v>
+        <v>78.18188797937262</v>
       </c>
       <c r="H243" t="n">
-        <v>4.657913275941738e-16</v>
+        <v>4.43329544266233e-16</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>10000</v>
       </c>
       <c r="C244" t="n">
-        <v>9998.498729905592</v>
+        <v>9999.325786609601</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14562,16 +14562,16 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1800.14802212025</v>
+        <v>1827.609287784684</v>
       </c>
       <c r="F244" t="n">
-        <v>0.180014802212025</v>
+        <v>0.1827609287784684</v>
       </c>
       <c r="G244" t="n">
-        <v>80.88480660060117</v>
+        <v>81.87273763304621</v>
       </c>
       <c r="H244" t="n">
-        <v>4.725706197584344e-16</v>
+        <v>4.266352090689571e-16</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>10000</v>
       </c>
       <c r="C245" t="n">
-        <v>9998.498729905592</v>
+        <v>9999.325786609601</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14620,16 +14620,16 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1632.447441921809</v>
+        <v>1636.595137281975</v>
       </c>
       <c r="F245" t="n">
-        <v>0.1632447441921809</v>
+        <v>0.1636595137281975</v>
       </c>
       <c r="G245" t="n">
-        <v>80.88480660060117</v>
+        <v>81.87273763304621</v>
       </c>
       <c r="H245" t="n">
-        <v>4.725706197584344e-16</v>
+        <v>4.266352090689571e-16</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>10000</v>
       </c>
       <c r="C246" t="n">
-        <v>10000.75929734944</v>
+        <v>9999.706991610434</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14678,16 +14678,16 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1781.125631645145</v>
+        <v>1800.269628207507</v>
       </c>
       <c r="F246" t="n">
-        <v>0.1781125631645145</v>
+        <v>0.1800269628207507</v>
       </c>
       <c r="G246" t="n">
-        <v>83.91648547786393</v>
+        <v>83.77425156882327</v>
       </c>
       <c r="H246" t="n">
-        <v>4.646445592472231e-16</v>
+        <v>4.556067645335914e-16</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>10000</v>
       </c>
       <c r="C247" t="n">
-        <v>10000.75929734944</v>
+        <v>9999.706991610434</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -14736,16 +14736,16 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1616.148330672806</v>
+        <v>1624.451419525022</v>
       </c>
       <c r="F247" t="n">
-        <v>0.1616148330672806</v>
+        <v>0.1624451419525022</v>
       </c>
       <c r="G247" t="n">
-        <v>83.91648547786393</v>
+        <v>83.77425156882327</v>
       </c>
       <c r="H247" t="n">
-        <v>4.646445592472231e-16</v>
+        <v>4.556067645335914e-16</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>10000</v>
       </c>
       <c r="C248" t="n">
-        <v>10000.49428883955</v>
+        <v>9999.737572920474</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -14794,16 +14794,16 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1794.736241433621</v>
+        <v>1792.95977015905</v>
       </c>
       <c r="F248" t="n">
-        <v>0.1794736241433621</v>
+        <v>0.179295977015905</v>
       </c>
       <c r="G248" t="n">
-        <v>84.89898071160262</v>
+        <v>82.15961562303815</v>
       </c>
       <c r="H248" t="n">
-        <v>4.650641191087737e-16</v>
+        <v>4.606409497105146e-16</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>10000</v>
       </c>
       <c r="C249" t="n">
-        <v>10000.49428883955</v>
+        <v>9999.737572920474</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -14852,16 +14852,16 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1617.613678772352</v>
+        <v>1603.472818757139</v>
       </c>
       <c r="F249" t="n">
-        <v>0.1617613678772352</v>
+        <v>0.1603472818757139</v>
       </c>
       <c r="G249" t="n">
-        <v>84.89898071160262</v>
+        <v>82.15961562303815</v>
       </c>
       <c r="H249" t="n">
-        <v>4.650641191087737e-16</v>
+        <v>4.606409497105146e-16</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>10000</v>
       </c>
       <c r="C250" t="n">
-        <v>10002.24316488427</v>
+        <v>9999.667959624199</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -14910,16 +14910,16 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1799.419180554733</v>
+        <v>1762.53301559931</v>
       </c>
       <c r="F250" t="n">
-        <v>0.1799419180554733</v>
+        <v>0.176253301559931</v>
       </c>
       <c r="G250" t="n">
-        <v>80.6828692606471</v>
+        <v>87.37832518706672</v>
       </c>
       <c r="H250" t="n">
-        <v>4.417782006319776e-16</v>
+        <v>4.425642497753779e-16</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>10000</v>
       </c>
       <c r="C251" t="n">
-        <v>10002.24316488427</v>
+        <v>9999.667959624199</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -14968,16 +14968,16 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1635.854858099473</v>
+        <v>1592.940432419757</v>
       </c>
       <c r="F251" t="n">
-        <v>0.1635854858099473</v>
+        <v>0.1592940432419757</v>
       </c>
       <c r="G251" t="n">
-        <v>80.6828692606471</v>
+        <v>87.37832518706672</v>
       </c>
       <c r="H251" t="n">
-        <v>4.417782006319776e-16</v>
+        <v>4.425642497753779e-16</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>10000</v>
       </c>
       <c r="C252" t="n">
-        <v>9999.085723908367</v>
+        <v>10000.38655953548</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15026,16 +15026,16 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1775.808857887316</v>
+        <v>1782.827813963587</v>
       </c>
       <c r="F252" t="n">
-        <v>0.1775808857887315</v>
+        <v>0.1782827813963587</v>
       </c>
       <c r="G252" t="n">
-        <v>85.8992390580767</v>
+        <v>86.44254236297165</v>
       </c>
       <c r="H252" t="n">
-        <v>4.478675662538569e-16</v>
+        <v>4.551119213888126e-16</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>10000</v>
       </c>
       <c r="C253" t="n">
-        <v>9999.085723908367</v>
+        <v>10000.38655953548</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15084,16 +15084,16 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1602.341946453119</v>
+        <v>1615.102598292564</v>
       </c>
       <c r="F253" t="n">
-        <v>0.1602341946453119</v>
+        <v>0.1615102598292564</v>
       </c>
       <c r="G253" t="n">
-        <v>85.8992390580767</v>
+        <v>86.44254236297165</v>
       </c>
       <c r="H253" t="n">
-        <v>4.478675662538569e-16</v>
+        <v>4.551119213888126e-16</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>10000</v>
       </c>
       <c r="C254" t="n">
-        <v>9999.325307417661</v>
+        <v>9999.131840507627</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15142,16 +15142,16 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>1844.835524770138</v>
+        <v>1766.649113564319</v>
       </c>
       <c r="F254" t="n">
-        <v>0.1844835524770138</v>
+        <v>0.1766649113564319</v>
       </c>
       <c r="G254" t="n">
-        <v>81.91995121160643</v>
+        <v>83.14968462263187</v>
       </c>
       <c r="H254" t="n">
-        <v>4.613561751534422e-16</v>
+        <v>4.624205189239271e-16</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>10000</v>
       </c>
       <c r="C255" t="n">
-        <v>9999.325307417661</v>
+        <v>9999.131840507627</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15200,16 +15200,16 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1659.918153971733</v>
+        <v>1594.5585258312</v>
       </c>
       <c r="F255" t="n">
-        <v>0.1659918153971733</v>
+        <v>0.15945585258312</v>
       </c>
       <c r="G255" t="n">
-        <v>81.91995121160643</v>
+        <v>83.14968462263187</v>
       </c>
       <c r="H255" t="n">
-        <v>4.613561751534422e-16</v>
+        <v>4.624205189239271e-16</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>10000</v>
       </c>
       <c r="C256" t="n">
-        <v>9998.647686317528</v>
+        <v>9998.414538762818</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15258,16 +15258,16 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1867.244434026461</v>
+        <v>1880.803024298508</v>
       </c>
       <c r="F256" t="n">
-        <v>0.1867244434026461</v>
+        <v>0.1880803024298508</v>
       </c>
       <c r="G256" t="n">
-        <v>74.0412537549192</v>
+        <v>70.64638106245891</v>
       </c>
       <c r="H256" t="n">
-        <v>4.330338286562236e-16</v>
+        <v>4.127311591070599e-16</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>10000</v>
       </c>
       <c r="C257" t="n">
-        <v>9998.647686317528</v>
+        <v>9998.414538762818</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15316,16 +15316,16 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>1688.916908356262</v>
+        <v>1681.978247286486</v>
       </c>
       <c r="F257" t="n">
-        <v>0.1688916908356262</v>
+        <v>0.1681978247286486</v>
       </c>
       <c r="G257" t="n">
-        <v>74.0412537549192</v>
+        <v>70.64638106245891</v>
       </c>
       <c r="H257" t="n">
-        <v>4.330338286562236e-16</v>
+        <v>4.127311591070599e-16</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>10000</v>
       </c>
       <c r="C258" t="n">
-        <v>9998.589611321026</v>
+        <v>10000.77101408982</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15374,16 +15374,16 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>1830.695541417784</v>
+        <v>1797.042422515134</v>
       </c>
       <c r="F258" t="n">
-        <v>0.1830695541417784</v>
+        <v>0.1797042422515134</v>
       </c>
       <c r="G258" t="n">
-        <v>81.38938239959641</v>
+        <v>85.41150694703279</v>
       </c>
       <c r="H258" t="n">
-        <v>4.73672018924694e-16</v>
+        <v>4.533282672987253e-16</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>10000</v>
       </c>
       <c r="C259" t="n">
-        <v>9998.589611321026</v>
+        <v>10000.77101408982</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15432,16 +15432,16 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>1654.719229078483</v>
+        <v>1600.941275227636</v>
       </c>
       <c r="F259" t="n">
-        <v>0.1654719229078483</v>
+        <v>0.1600941275227636</v>
       </c>
       <c r="G259" t="n">
-        <v>81.38938239959641</v>
+        <v>85.41150694703279</v>
       </c>
       <c r="H259" t="n">
-        <v>4.73672018924694e-16</v>
+        <v>4.533282672987253e-16</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>10000</v>
       </c>
       <c r="C260" t="n">
-        <v>9998.831933171641</v>
+        <v>9998.818722946269</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15490,16 +15490,16 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>1887.478771720854</v>
+        <v>1786.399119209481</v>
       </c>
       <c r="F260" t="n">
-        <v>0.1887478771720854</v>
+        <v>0.1786399119209481</v>
       </c>
       <c r="G260" t="n">
-        <v>72.20863920080978</v>
+        <v>78.48255226433697</v>
       </c>
       <c r="H260" t="n">
-        <v>4.500646406521671e-16</v>
+        <v>4.422580008893017e-16</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>10000</v>
       </c>
       <c r="C261" t="n">
-        <v>9998.831933171641</v>
+        <v>9998.818722946269</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15548,16 +15548,16 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1701.371480737923</v>
+        <v>1619.760791162156</v>
       </c>
       <c r="F261" t="n">
-        <v>0.1701371480737923</v>
+        <v>0.1619760791162156</v>
       </c>
       <c r="G261" t="n">
-        <v>72.20863920080978</v>
+        <v>78.48255226433697</v>
       </c>
       <c r="H261" t="n">
-        <v>4.500646406521671e-16</v>
+        <v>4.422580008893017e-16</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>10000</v>
       </c>
       <c r="C262" t="n">
-        <v>9999.998108600546</v>
+        <v>9998.787708899135</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15606,16 +15606,16 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>2105.888220544502</v>
+        <v>2120.123731521247</v>
       </c>
       <c r="F262" t="n">
-        <v>0.2105888220544502</v>
+        <v>0.2120123731521248</v>
       </c>
       <c r="G262" t="n">
-        <v>63.19899464903692</v>
+        <v>61.06785107617866</v>
       </c>
       <c r="H262" t="n">
-        <v>8.152067840384967e-16</v>
+        <v>8.15381694430976e-16</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>10000</v>
       </c>
       <c r="C263" t="n">
-        <v>9999.998108600546</v>
+        <v>9998.787708899135</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15664,16 +15664,16 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>1904.016549656003</v>
+        <v>1921.805561460304</v>
       </c>
       <c r="F263" t="n">
-        <v>0.1904016549656003</v>
+        <v>0.1921805561460304</v>
       </c>
       <c r="G263" t="n">
-        <v>63.19899464903692</v>
+        <v>61.06785107617866</v>
       </c>
       <c r="H263" t="n">
-        <v>8.152067840384967e-16</v>
+        <v>8.15381694430976e-16</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>10000</v>
       </c>
       <c r="C264" t="n">
-        <v>10000.31227904316</v>
+        <v>10000.39195788624</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15722,16 +15722,16 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>2060.631621824163</v>
+        <v>2121.172608661921</v>
       </c>
       <c r="F264" t="n">
-        <v>0.2060631621824163</v>
+        <v>0.2121172608661921</v>
       </c>
       <c r="G264" t="n">
-        <v>63.77681779384075</v>
+        <v>60.8006667420538</v>
       </c>
       <c r="H264" t="n">
-        <v>8.10374913301563e-16</v>
+        <v>8.329561114081484e-16</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>10000</v>
       </c>
       <c r="C265" t="n">
-        <v>10000.31227904316</v>
+        <v>10000.39195788624</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -15780,16 +15780,16 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>1874.000931287087</v>
+        <v>1900.378850263942</v>
       </c>
       <c r="F265" t="n">
-        <v>0.1874000931287088</v>
+        <v>0.1900378850263942</v>
       </c>
       <c r="G265" t="n">
-        <v>63.77681779384075</v>
+        <v>60.8006667420538</v>
       </c>
       <c r="H265" t="n">
-        <v>8.10374913301563e-16</v>
+        <v>8.329561114081484e-16</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>10000</v>
       </c>
       <c r="C266" t="n">
-        <v>9999.973592165021</v>
+        <v>10000.88483172542</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -15838,16 +15838,16 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>2115.540293671532</v>
+        <v>2112.279814035129</v>
       </c>
       <c r="F266" t="n">
-        <v>0.2115540293671532</v>
+        <v>0.2112279814035129</v>
       </c>
       <c r="G266" t="n">
-        <v>61.14045926144784</v>
+        <v>63.2906427817862</v>
       </c>
       <c r="H266" t="n">
-        <v>8.268389287895991e-16</v>
+        <v>8.087039393920229e-16</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>10000</v>
       </c>
       <c r="C267" t="n">
-        <v>9999.973592165021</v>
+        <v>10000.88483172542</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -15896,16 +15896,16 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>1923.049632648848</v>
+        <v>1882.648319946218</v>
       </c>
       <c r="F267" t="n">
-        <v>0.1923049632648848</v>
+        <v>0.1882648319946218</v>
       </c>
       <c r="G267" t="n">
-        <v>61.14045926144784</v>
+        <v>63.2906427817862</v>
       </c>
       <c r="H267" t="n">
-        <v>8.268389287895991e-16</v>
+        <v>8.087039393920229e-16</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>10000</v>
       </c>
       <c r="C268" t="n">
-        <v>9999.987490468799</v>
+        <v>9999.510186085554</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -15954,16 +15954,16 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>2152.768729156583</v>
+        <v>2067.716163112711</v>
       </c>
       <c r="F268" t="n">
-        <v>0.2152768729156583</v>
+        <v>0.2067716163112711</v>
       </c>
       <c r="G268" t="n">
-        <v>55.32899133045665</v>
+        <v>63.54084746024429</v>
       </c>
       <c r="H268" t="n">
-        <v>7.541438425063795e-16</v>
+        <v>8.057055952288248e-16</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>10000</v>
       </c>
       <c r="C269" t="n">
-        <v>9999.987490468799</v>
+        <v>9999.510186085554</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16012,16 +16012,16 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>1954.455886645319</v>
+        <v>1862.913628626374</v>
       </c>
       <c r="F269" t="n">
-        <v>0.1954455886645319</v>
+        <v>0.1862913628626374</v>
       </c>
       <c r="G269" t="n">
-        <v>55.32899133045665</v>
+        <v>63.54084746024429</v>
       </c>
       <c r="H269" t="n">
-        <v>7.541438425063795e-16</v>
+        <v>8.057055952288248e-16</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>10000</v>
       </c>
       <c r="C270" t="n">
-        <v>9999.548991060348</v>
+        <v>10000.14351901047</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16070,16 +16070,16 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>2138.032931873912</v>
+        <v>2139.426375122332</v>
       </c>
       <c r="F270" t="n">
-        <v>0.2138032931873912</v>
+        <v>0.2139426375122332</v>
       </c>
       <c r="G270" t="n">
-        <v>59.42526906014366</v>
+        <v>60.56674559638198</v>
       </c>
       <c r="H270" t="n">
-        <v>8.283924645792151e-16</v>
+        <v>8.422532943040061e-16</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>10000</v>
       </c>
       <c r="C271" t="n">
-        <v>9999.548991060348</v>
+        <v>10000.14351901047</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16128,16 +16128,16 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1923.185783715278</v>
+        <v>1924.074883970142</v>
       </c>
       <c r="F271" t="n">
-        <v>0.1923185783715278</v>
+        <v>0.1924074883970142</v>
       </c>
       <c r="G271" t="n">
-        <v>59.42526906014366</v>
+        <v>60.56674559638198</v>
       </c>
       <c r="H271" t="n">
-        <v>8.283924645792151e-16</v>
+        <v>8.422532943040061e-16</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>10000</v>
       </c>
       <c r="C272" t="n">
-        <v>9999.887911168938</v>
+        <v>10000.06186435517</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16186,16 +16186,16 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>2075.811533377163</v>
+        <v>2019.047337138021</v>
       </c>
       <c r="F272" t="n">
-        <v>0.2075811533377162</v>
+        <v>0.2019047337138021</v>
       </c>
       <c r="G272" t="n">
-        <v>62.08641261485643</v>
+        <v>64.05102906013315</v>
       </c>
       <c r="H272" t="n">
-        <v>8.368819730501869e-16</v>
+        <v>8.035360251501696e-16</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>10000</v>
       </c>
       <c r="C273" t="n">
-        <v>9999.887911168938</v>
+        <v>10000.06186435517</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16244,16 +16244,16 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1885.341831673703</v>
+        <v>1846.344505513304</v>
       </c>
       <c r="F273" t="n">
-        <v>0.1885341831673703</v>
+        <v>0.1846344505513304</v>
       </c>
       <c r="G273" t="n">
-        <v>62.08641261485643</v>
+        <v>64.05102906013315</v>
       </c>
       <c r="H273" t="n">
-        <v>8.368819730501869e-16</v>
+        <v>8.035360251501696e-16</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>10000</v>
       </c>
       <c r="C274" t="n">
-        <v>9998.663882794113</v>
+        <v>10000.98747779685</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16302,16 +16302,16 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>2053.119744090711</v>
+        <v>2098.31252613963</v>
       </c>
       <c r="F274" t="n">
-        <v>0.2053119744090711</v>
+        <v>0.209831252613963</v>
       </c>
       <c r="G274" t="n">
-        <v>62.04071400832935</v>
+        <v>62.39656683453057</v>
       </c>
       <c r="H274" t="n">
-        <v>8.051288116002457e-16</v>
+        <v>8.322348572206609e-16</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>10000</v>
       </c>
       <c r="C275" t="n">
-        <v>9998.663882794113</v>
+        <v>10000.98747779685</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16360,16 +16360,16 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>1849.281923976075</v>
+        <v>1875.703934776837</v>
       </c>
       <c r="F275" t="n">
-        <v>0.1849281923976075</v>
+        <v>0.1875703934776837</v>
       </c>
       <c r="G275" t="n">
-        <v>62.04071400832935</v>
+        <v>62.39656683453057</v>
       </c>
       <c r="H275" t="n">
-        <v>8.051288116002457e-16</v>
+        <v>8.322348572206609e-16</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>10000</v>
       </c>
       <c r="C276" t="n">
-        <v>9999.947592476703</v>
+        <v>9999.491106624098</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16418,16 +16418,16 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>2073.272634974893</v>
+        <v>2095.255319131545</v>
       </c>
       <c r="F276" t="n">
-        <v>0.2073272634974893</v>
+        <v>0.2095255319131545</v>
       </c>
       <c r="G276" t="n">
-        <v>64.01017604508911</v>
+        <v>62.16014911296374</v>
       </c>
       <c r="H276" t="n">
-        <v>8.096737060107939e-16</v>
+        <v>8.408418099182094e-16</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>10000</v>
       </c>
       <c r="C277" t="n">
-        <v>9999.947592476703</v>
+        <v>9999.491106624098</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16476,16 +16476,16 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>1869.173329361692</v>
+        <v>1873.2699591283</v>
       </c>
       <c r="F277" t="n">
-        <v>0.1869173329361692</v>
+        <v>0.18732699591283</v>
       </c>
       <c r="G277" t="n">
-        <v>64.01017604508911</v>
+        <v>62.16014911296374</v>
       </c>
       <c r="H277" t="n">
-        <v>8.096737060107939e-16</v>
+        <v>8.408418099182094e-16</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>10000</v>
       </c>
       <c r="C278" t="n">
-        <v>10000.12585704884</v>
+        <v>9998.852345099551</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16534,16 +16534,16 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>2127.590801619958</v>
+        <v>2119.086897062622</v>
       </c>
       <c r="F278" t="n">
-        <v>0.2127590801619958</v>
+        <v>0.2119086897062621</v>
       </c>
       <c r="G278" t="n">
-        <v>58.51075739344328</v>
+        <v>62.75045023992437</v>
       </c>
       <c r="H278" t="n">
-        <v>7.947589896236367e-16</v>
+        <v>8.143038842682787e-16</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>10000</v>
       </c>
       <c r="C279" t="n">
-        <v>10000.12585704884</v>
+        <v>9998.852345099551</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16592,16 +16592,16 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>1929.064708109298</v>
+        <v>1905.421244275385</v>
       </c>
       <c r="F279" t="n">
-        <v>0.1929064708109298</v>
+        <v>0.1905421244275385</v>
       </c>
       <c r="G279" t="n">
-        <v>58.51075739344328</v>
+        <v>62.75045023992437</v>
       </c>
       <c r="H279" t="n">
-        <v>7.947589896236367e-16</v>
+        <v>8.143038842682787e-16</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>10000</v>
       </c>
       <c r="C280" t="n">
-        <v>10000.88931028984</v>
+        <v>9999.275553750073</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16650,16 +16650,16 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>2049.610775347343</v>
+        <v>2129.74644777853</v>
       </c>
       <c r="F280" t="n">
-        <v>0.2049610775347344</v>
+        <v>0.212974644777853</v>
       </c>
       <c r="G280" t="n">
-        <v>64.05885549556417</v>
+        <v>55.54732258695</v>
       </c>
       <c r="H280" t="n">
-        <v>7.958833627736571e-16</v>
+        <v>7.812267491342535e-16</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>10000</v>
       </c>
       <c r="C281" t="n">
-        <v>10000.88931028984</v>
+        <v>9999.275553750073</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16708,16 +16708,16 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>1858.994579622358</v>
+        <v>1923.320364029695</v>
       </c>
       <c r="F281" t="n">
-        <v>0.1858994579622358</v>
+        <v>0.1923320364029695</v>
       </c>
       <c r="G281" t="n">
-        <v>64.05885549556417</v>
+        <v>55.54732258695</v>
       </c>
       <c r="H281" t="n">
-        <v>7.958833627736571e-16</v>
+        <v>7.812267491342535e-16</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>10000</v>
       </c>
       <c r="C282" t="n">
-        <v>10000.1239147986</v>
+        <v>9999.483242610333</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -16766,16 +16766,16 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>2304.874292588561</v>
+        <v>2307.385810490789</v>
       </c>
       <c r="F282" t="n">
-        <v>0.2304874292588561</v>
+        <v>0.2307385810490789</v>
       </c>
       <c r="G282" t="n">
-        <v>50.26040432164013</v>
+        <v>49.52441083261109</v>
       </c>
       <c r="H282" t="n">
-        <v>1.281384246883485e-15</v>
+        <v>1.279681250525406e-15</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>10000</v>
       </c>
       <c r="C283" t="n">
-        <v>10000.1239147986</v>
+        <v>9999.483242610333</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -16824,16 +16824,16 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>2100.72460955878</v>
+        <v>2092.814327637634</v>
       </c>
       <c r="F283" t="n">
-        <v>0.210072460955878</v>
+        <v>0.2092814327637634</v>
       </c>
       <c r="G283" t="n">
-        <v>50.26040432164013</v>
+        <v>49.52441083261109</v>
       </c>
       <c r="H283" t="n">
-        <v>1.281384246883485e-15</v>
+        <v>1.279681250525406e-15</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>10000</v>
       </c>
       <c r="C284" t="n">
-        <v>10000.13335951224</v>
+        <v>9999.228572651149</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -16882,16 +16882,16 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>2331.416629863299</v>
+        <v>2292.22814806695</v>
       </c>
       <c r="F284" t="n">
-        <v>0.23314166298633</v>
+        <v>0.229222814806695</v>
       </c>
       <c r="G284" t="n">
-        <v>49.0503778185554</v>
+        <v>50.03067030215671</v>
       </c>
       <c r="H284" t="n">
-        <v>1.288403976948226e-15</v>
+        <v>1.215252729373155e-15</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>10000</v>
       </c>
       <c r="C285" t="n">
-        <v>10000.13335951224</v>
+        <v>9999.228572651149</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -16940,16 +16940,16 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>2110.303714073078</v>
+        <v>2079.523493453076</v>
       </c>
       <c r="F285" t="n">
-        <v>0.2110303714073077</v>
+        <v>0.2079523493453076</v>
       </c>
       <c r="G285" t="n">
-        <v>49.0503778185554</v>
+        <v>50.03067030215671</v>
       </c>
       <c r="H285" t="n">
-        <v>1.288403976948226e-15</v>
+        <v>1.215252729373155e-15</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>10000</v>
       </c>
       <c r="C286" t="n">
-        <v>9999.679608735078</v>
+        <v>10000.51905806508</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -16998,16 +16998,16 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>2395.555915282052</v>
+        <v>2367.088854616246</v>
       </c>
       <c r="F286" t="n">
-        <v>0.2395555915282052</v>
+        <v>0.2367088854616246</v>
       </c>
       <c r="G286" t="n">
-        <v>47.33858506174307</v>
+        <v>49.62041644191532</v>
       </c>
       <c r="H286" t="n">
-        <v>1.282724267069963e-15</v>
+        <v>1.296102434711598e-15</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>10000</v>
       </c>
       <c r="C287" t="n">
-        <v>9999.679608735078</v>
+        <v>10000.51905806508</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17056,16 +17056,16 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>2168.66030568917</v>
+        <v>2136.27608542146</v>
       </c>
       <c r="F287" t="n">
-        <v>0.216866030568917</v>
+        <v>0.213627608542146</v>
       </c>
       <c r="G287" t="n">
-        <v>47.33858506174307</v>
+        <v>49.62041644191532</v>
       </c>
       <c r="H287" t="n">
-        <v>1.282724267069963e-15</v>
+        <v>1.296102434711598e-15</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>10000</v>
       </c>
       <c r="C288" t="n">
-        <v>9999.50726773221</v>
+        <v>9999.065954518481</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17114,16 +17114,16 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>2359.145827382985</v>
+        <v>2371.81089965392</v>
       </c>
       <c r="F288" t="n">
-        <v>0.2359145827382985</v>
+        <v>0.237181089965392</v>
       </c>
       <c r="G288" t="n">
-        <v>47.95645981100107</v>
+        <v>49.34858975434953</v>
       </c>
       <c r="H288" t="n">
-        <v>1.24667684664921e-15</v>
+        <v>1.26999449205568e-15</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>10000</v>
       </c>
       <c r="C289" t="n">
-        <v>9999.50726773221</v>
+        <v>9999.065954518481</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17172,16 +17172,16 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>2113.747456273283</v>
+        <v>2115.821566623014</v>
       </c>
       <c r="F289" t="n">
-        <v>0.2113747456273283</v>
+        <v>0.2115821566623014</v>
       </c>
       <c r="G289" t="n">
-        <v>47.95645981100107</v>
+        <v>49.34858975434953</v>
       </c>
       <c r="H289" t="n">
-        <v>1.24667684664921e-15</v>
+        <v>1.26999449205568e-15</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>10000</v>
       </c>
       <c r="C290" t="n">
-        <v>10000.44286963795</v>
+        <v>9999.244127096075</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17230,16 +17230,16 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>2322.175475517191</v>
+        <v>2330.667214802082</v>
       </c>
       <c r="F290" t="n">
-        <v>0.2322175475517192</v>
+        <v>0.2330667214802082</v>
       </c>
       <c r="G290" t="n">
-        <v>51.85951578173412</v>
+        <v>50.36416028948057</v>
       </c>
       <c r="H290" t="n">
-        <v>1.272786561034445e-15</v>
+        <v>1.284757991068691e-15</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>10000</v>
       </c>
       <c r="C291" t="n">
-        <v>10000.44286963795</v>
+        <v>9999.244127096075</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17288,16 +17288,16 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>2068.095097442823</v>
+        <v>2081.828399506262</v>
       </c>
       <c r="F291" t="n">
-        <v>0.2068095097442823</v>
+        <v>0.2081828399506262</v>
       </c>
       <c r="G291" t="n">
-        <v>51.85951578173412</v>
+        <v>50.36416028948057</v>
       </c>
       <c r="H291" t="n">
-        <v>1.272786561034445e-15</v>
+        <v>1.284757991068691e-15</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>10000</v>
       </c>
       <c r="C292" t="n">
-        <v>9999.386019826121</v>
+        <v>9999.724818951576</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17346,16 +17346,16 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>2436.014550901697</v>
+        <v>2371.909405497299</v>
       </c>
       <c r="F292" t="n">
-        <v>0.2436014550901698</v>
+        <v>0.2371909405497299</v>
       </c>
       <c r="G292" t="n">
-        <v>42.37654622770141</v>
+        <v>48.7282514443568</v>
       </c>
       <c r="H292" t="n">
-        <v>1.26715859976492e-15</v>
+        <v>1.324778448997269e-15</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>10000</v>
       </c>
       <c r="C293" t="n">
-        <v>9999.386019826121</v>
+        <v>9999.724818951576</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17404,16 +17404,16 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>2203.442164021471</v>
+        <v>2140.555634062187</v>
       </c>
       <c r="F293" t="n">
-        <v>0.2203442164021471</v>
+        <v>0.2140555634062187</v>
       </c>
       <c r="G293" t="n">
-        <v>42.37654622770141</v>
+        <v>48.7282514443568</v>
       </c>
       <c r="H293" t="n">
-        <v>1.26715859976492e-15</v>
+        <v>1.324778448997269e-15</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>10000</v>
       </c>
       <c r="C294" t="n">
-        <v>10000.32108052216</v>
+        <v>10000.14204257232</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17462,16 +17462,16 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>2348.544210391088</v>
+        <v>2397.639511636318</v>
       </c>
       <c r="F294" t="n">
-        <v>0.2348544210391088</v>
+        <v>0.2397639511636318</v>
       </c>
       <c r="G294" t="n">
-        <v>48.4750777548805</v>
+        <v>47.58578957733833</v>
       </c>
       <c r="H294" t="n">
-        <v>1.324841257691927e-15</v>
+        <v>1.259212994919593e-15</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>10000</v>
       </c>
       <c r="C295" t="n">
-        <v>10000.32108052216</v>
+        <v>10000.14204257232</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17520,16 +17520,16 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>2095.92368180971</v>
+        <v>2160.780909989905</v>
       </c>
       <c r="F295" t="n">
-        <v>0.209592368180971</v>
+        <v>0.2160780909989905</v>
       </c>
       <c r="G295" t="n">
-        <v>48.4750777548805</v>
+        <v>47.58578957733833</v>
       </c>
       <c r="H295" t="n">
-        <v>1.324841257691927e-15</v>
+        <v>1.259212994919593e-15</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>10000</v>
       </c>
       <c r="C296" t="n">
-        <v>9999.98865199285</v>
+        <v>10001.1949282591</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17578,16 +17578,16 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>2379.595619788524</v>
+        <v>2414.175958758297</v>
       </c>
       <c r="F296" t="n">
-        <v>0.2379595619788524</v>
+        <v>0.2414175958758297</v>
       </c>
       <c r="G296" t="n">
-        <v>50.7688829429114</v>
+        <v>47.26851798588712</v>
       </c>
       <c r="H296" t="n">
-        <v>1.26614654913586e-15</v>
+        <v>1.252832560777901e-15</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>10000</v>
       </c>
       <c r="C297" t="n">
-        <v>9999.98865199285</v>
+        <v>10001.1949282591</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17636,16 +17636,16 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>2127.823522617799</v>
+        <v>2199.447259610031</v>
       </c>
       <c r="F297" t="n">
-        <v>0.2127823522617799</v>
+        <v>0.2199447259610031</v>
       </c>
       <c r="G297" t="n">
-        <v>50.7688829429114</v>
+        <v>47.26851798588712</v>
       </c>
       <c r="H297" t="n">
-        <v>1.26614654913586e-15</v>
+        <v>1.252832560777901e-15</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>10000</v>
       </c>
       <c r="C298" t="n">
-        <v>10000.90352765968</v>
+        <v>10000.89225791721</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17694,16 +17694,16 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>2339.640416992718</v>
+        <v>2379.591166723663</v>
       </c>
       <c r="F298" t="n">
-        <v>0.2339640416992718</v>
+        <v>0.2379591166723663</v>
       </c>
       <c r="G298" t="n">
-        <v>50.33564476383119</v>
+        <v>47.65617315092886</v>
       </c>
       <c r="H298" t="n">
-        <v>1.265733717596201e-15</v>
+        <v>1.297295654110043e-15</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
@@ -17744,7 +17744,7 @@
         <v>10000</v>
       </c>
       <c r="C299" t="n">
-        <v>10000.90352765968</v>
+        <v>10000.89225791721</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -17752,16 +17752,16 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>2121.447245900457</v>
+        <v>2144.595604072733</v>
       </c>
       <c r="F299" t="n">
-        <v>0.2121447245900457</v>
+        <v>0.2144595604072733</v>
       </c>
       <c r="G299" t="n">
-        <v>50.33564476383119</v>
+        <v>47.65617315092886</v>
       </c>
       <c r="H299" t="n">
-        <v>1.265733717596201e-15</v>
+        <v>1.297295654110043e-15</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>10000</v>
       </c>
       <c r="C300" t="n">
-        <v>9999.210226966719</v>
+        <v>9999.971658619808</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -17810,16 +17810,16 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>2325.189567848261</v>
+        <v>2378.671747228692</v>
       </c>
       <c r="F300" t="n">
-        <v>0.2325189567848261</v>
+        <v>0.2378671747228692</v>
       </c>
       <c r="G300" t="n">
-        <v>50.04204863644895</v>
+        <v>47.67354814212924</v>
       </c>
       <c r="H300" t="n">
-        <v>1.30214039396546e-15</v>
+        <v>1.242664866309666e-15</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>10000</v>
       </c>
       <c r="C301" t="n">
-        <v>9999.210226966719</v>
+        <v>9999.971658619808</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -17868,16 +17868,16 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>2113.775444711686</v>
+        <v>2157.197821642435</v>
       </c>
       <c r="F301" t="n">
-        <v>0.2113775444711686</v>
+        <v>0.2157197821642436</v>
       </c>
       <c r="G301" t="n">
-        <v>50.04204863644895</v>
+        <v>47.67354814212924</v>
       </c>
       <c r="H301" t="n">
-        <v>1.30214039396546e-15</v>
+        <v>1.242664866309666e-15</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>

--- a/results/NDDHO N_xi Data [T_xi_len_s=25, Qs=[20, 40, 60, 80, 100], int 25ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
+++ b/results/NDDHO N_xi Data [T_xi_len_s=25, Qs=[20, 40, 60, 80, 100], int 25ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -11078,7 +11078,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -12934,7 +12934,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -14210,7 +14210,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E240" t="n">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E264" t="n">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E266" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E272" t="n">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E276" t="n">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E278" t="n">
@@ -16646,7 +16646,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -16762,7 +16762,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -16994,7 +16994,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -17110,7 +17110,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -17342,7 +17342,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -17458,7 +17458,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E298" t="n">
@@ -17806,7 +17806,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E300" t="n">
